--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png?v=3623a09a3d</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -535,7 +535,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png?v=66392bb8b2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -570,10 +570,10 @@
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>1710</v>
+        <v>1665</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png?v=853ce5f975|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png?v=01ff072142|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png?v=5bada80f79</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=7ea3564566|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png?v=925edc897f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png?v=2dddb3884d</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png?v=23bde7d308</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -841,7 +841,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png?v=ef9e5c1565</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png?v=8bec31bf8f</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -902,7 +902,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png?v=558065bb93|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png?v=34e4e88bf6</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png?v=e49b0e06dd</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=1d88443a00|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png?v=c5312dc0b8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png?v=92f41095e4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png?v=ed43613b04</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png?v=207791c0ab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png?v=8522c1e191|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png?v=a72d637b33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png?v=5a785335c2</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png?v=9a506331a9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png?v=45a69e38a1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png?v=4b4f837537|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png?v=e1488b6f03</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=936073c4cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png?v=4ec9bb8ca0|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png?v=838071f395|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png?v=b93ad38a77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png?v=4f093a4b63</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png?v=fc60a3cbb2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png?v=42835ce71d</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=7cb0bd4a20</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png?v=9a4139b864</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png?v=2ec99b161d</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg?v=e0223e07fa</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png?v=04fb90265c</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png?v=462ec457c3</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png?v=c48648e856</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png?v=3fb6a6ed69</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png?v=997df2de75</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png?v=9f571585c3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png?v=9fbf2bb6f0</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png?v=9e53670a82</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png?v=8cfd86455e</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg?v=dc356035c7</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png?v=6ac791003d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png?v=4bd4c0625c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png?v=4e011c48be</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png?v=c51183578d</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png?v=ee5f7fcab1</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TESTWB001_2.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TESTWB001_2.jpg?v=45a12b8349</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png?v=1d34e63372</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=648c289289</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$61</definedName>
@@ -504,7 +504,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png?v=3623a09a3d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -535,7 +535,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png?v=66392bb8b2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -570,10 +570,10 @@
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>1665</v>
+        <v>1710</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png?v=853ce5f975|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png?v=01ff072142|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png?v=5bada80f79</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=7ea3564566|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png?v=925edc897f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png?v=2dddb3884d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png?v=23bde7d308</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -841,7 +841,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png?v=ef9e5c1565</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Улучшенный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png?v=8bec31bf8f</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -902,7 +902,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png?v=558065bb93|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png?v=34e4e88bf6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png?v=e49b0e06dd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=1d88443a00|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png?v=c5312dc0b8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png?v=92f41095e4</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png?v=ed43613b04</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png?v=207791c0ab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png?v=8522c1e191|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png?v=a72d637b33</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png?v=5a785335c2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png?v=9a506331a9</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png?v=45a69e38a1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png?v=4b4f837537|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png?v=e1488b6f03</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=936073c4cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png?v=4ec9bb8ca0|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png?v=838071f395|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png?v=b93ad38a77</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png?v=4f093a4b63</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png?v=fc60a3cbb2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png?v=42835ce71d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=7cb0bd4a20</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png?v=9a4139b864</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png?v=2ec99b161d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg?v=e0223e07fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png?v=04fb90265c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png?v=462ec457c3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png?v=c48648e856</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png?v=3fb6a6ed69</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png?v=997df2de75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png?v=9f571585c3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png?v=9fbf2bb6f0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png?v=9e53670a82</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png?v=8cfd86455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg?v=dc356035c7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png?v=6ac791003d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png?v=4bd4c0625c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png?v=4e011c48be</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png?v=c51183578d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png?v=ee5f7fcab1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TESTWB001_2.jpg?v=45a12b8349</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TESTWB001_2.jpg</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png?v=1d34e63372</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=648c289289</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="n">
-        <v>2447.15</v>
+        <v>1450</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>15</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$61</definedName>
@@ -504,7 +504,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png?v=3623a09a3d</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -535,7 +535,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E.305.045_1.png?v=66392bb8b2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png?v=01ff072142|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png?v=5bada80f79</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=7ea3564566|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png?v=925edc897f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png?v=2dddb3884d</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png?v=23bde7d308</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -841,7 +841,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png?v=ef9e5c1565</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png?v=8bec31bf8f</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -902,7 +902,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png?v=558065bb93|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png?v=34e4e88bf6</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png?v=e49b0e06dd</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=1d88443a00|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png?v=c5312dc0b8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png?v=92f41095e4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png?v=ed43613b04</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_1.png?v=207791c0ab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_2.png?v=8522c1e191|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183B_3.png?v=a72d637b33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png?v=5a785335c2</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png?v=9a506331a9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png?v=45a69e38a1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png?v=4b4f837537|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png?v=e1488b6f03</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=936073c4cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png?v=4ec9bb8ca0|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png?v=838071f395|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png?v=b93ad38a77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png?v=4f093a4b63</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png?v=fc60a3cbb2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png?v=42835ce71d</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=7cb0bd4a20</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png?v=9a4139b864</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png?v=2ec99b161d</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg?v=e0223e07fa</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png?v=04fb90265c</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png?v=462ec457c3</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png?v=c48648e856</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png?v=3fb6a6ed69</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png?v=997df2de75</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png?v=9f571585c3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png?v=9fbf2bb6f0</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png?v=9e53670a82</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png?v=8cfd86455e</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://basket-34.wbbasket.ru/vol7115/part711557/711557492/images/big/1.webp</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.png?v=4beea95775</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg?v=dc356035c7</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png?v=6ac791003d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png?v=4bd4c0625c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png?v=4e011c48be</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png?v=c51183578d</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png?v=ee5f7fcab1</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TESTWB001_2.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/TESTWB001_2.jpg?v=45a12b8349</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png?v=1d34e63372</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=648c289289</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -540,10 +540,10 @@
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
     </row>
@@ -570,10 +570,10 @@
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>1710</v>
+        <v>1571.48</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=7ea3564566|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=7ea3564566</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="n">
-        <v>1450</v>
+        <v>2447.15</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>15</v>
@@ -2629,10 +2629,10 @@
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="n">
-        <v>1515.9</v>
+        <v>1418.1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
     </row>
@@ -2699,35 +2699,415 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).&lt;br/&gt;&lt;br/&gt; Новый, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Нужен максимальный ресурс? У нас есть улучшенная версия фильтра — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt; Артикул: filtr-dsg7-dq200.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=648c289289</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.png?v=b1ce9f5f30</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="n">
-        <v>15000</v>
+        <v>980</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>filtr-dsg7-dq500</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. Новый, с завода, в наличии, отправка в день заказа. Артикул: 0BH325183B.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="n">
+        <v>1290</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>jf011e</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников вариатора JF011E RE0F10A 4 шт оригинал</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.&lt;br/&gt;&lt;br/&gt;В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=648c289289</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>kryshka-mehatronika-dq200</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Совместима с 0AM325219C.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>plastina-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новая, с завода, отправка в день заказа.</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-dq200-2sht</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Пластины на соленоиды мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новые, с завода.</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-orig</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200,</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита + улучшенный фильтр за один заказ. Артикул плиты 0AM325066AE. Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.png?v=b8cb2f02a1</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Всё необходимое в одном заказе, только оригинальные расходники. Артикул плиты 0AM325066AE. Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.png?v=e34fb25bfd</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, к</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.png?v=fd0e412e14</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Нужен увеличенный ресурс? У нас есть усиленная (утолщённая) версия прокладки — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-kryshki-dq200.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-niz-dq200</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-niz-dq200.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-verh-dq200</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-verh-dq200.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>separatornaya-plastina-dq200</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новая, с завода, отправка в день заказа.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DS</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новые, с завода.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.&lt;br/&gt;&lt;br/&gt; Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.&lt;br/&gt;&lt;br/&gt; Восстановлен: проверен и протестирован перед отправкой.&lt;br/&gt;&lt;br/&gt; В наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: solenoid-02e-0b5-bolshoy.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H61"/>
+  <autoFilter ref="A1:H75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.png?v=b1ce9f5f30</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.png?v=b1ce9f5f30|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -2742,7 +2742,11 @@
           <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. Новый, с завода, в наличии, отправка в день заказа. Артикул: 0BH325183B.</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="n">
         <v>1290</v>
@@ -2798,7 +2802,11 @@
           <t>Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Совместима с 0AM325219C.</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.png?v=637a263fe5</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="n">
         <v>1950</v>
@@ -2824,7 +2832,11 @@
           <t>Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="n">
         <v>490</v>
@@ -2966,7 +2978,11 @@
           <t>Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Нужен увеличенный ресурс? У нас есть усиленная (утолщённая) версия прокладки — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-kryshki-dq200.</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="n">
         <v>1380</v>
@@ -2979,23 +2995,27 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-niz-dq200.</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новые, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-dq200.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="n">
-        <v>580</v>
+        <v>840</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>0</v>
@@ -3005,17 +3025,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-verh-dq200.</t>
+          <t>Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -3031,23 +3051,23 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
+          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новая, с завода, отправка в день заказа.</t>
+          <t>Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="n">
-        <v>490</v>
+        <v>580</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>0</v>
@@ -3057,23 +3077,27 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DS</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новые, с завода.</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новая, с завода, отправка в день заказа.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="n">
-        <v>1870</v>
+        <v>490</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>0</v>
@@ -3083,31 +3107,57 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DS</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.&lt;br/&gt;&lt;br/&gt; Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.&lt;br/&gt;&lt;br/&gt; Восстановлен: проверен и протестирован перед отправкой.&lt;br/&gt;&lt;br/&gt; В наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: solenoid-02e-0b5-bolshoy.</t>
+          <t>Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новые, с завода.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="n">
-        <v>5700</v>
+        <v>1870</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.&lt;br/&gt;&lt;br/&gt; Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.&lt;br/&gt;&lt;br/&gt; Восстановлен: проверен и протестирован перед отправкой.&lt;br/&gt;&lt;br/&gt; В наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: solenoid-02e-0b5-bolshoy.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H75"/>
+  <autoFilter ref="A1:H76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$76</definedName>
@@ -494,12 +494,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий</t>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X301127C</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество</t>
+          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Короткий&lt;br/&gt;&lt;br/&gt;Новый Отличное Качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 01X301127C.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -524,13 +524,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045+масляный фильтр DSG6</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 (02E305045) с масляным фильтром и уплотнительным кольцом для коробки передач DSG 6.
-Фильтр DSG6 обеспечивает очистку масла, снижает температуру и улучшает теплоотвод.</t>
+          <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045&lt;br/&gt;&lt;br/&gt;Резиновое кольцо в комплекте &lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Уменьшает температуру масла, улучшает теплоотвод</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -585,12 +584,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DQ250 02E DSG6</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество</t>
+          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -615,23 +614,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E305045</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный отвод тепла
-Уменьшает температуру масла КПП
-Резиновое кольцо в комплекте
-Алюминиевый корпус фильтра DSG6 DQ250 (02E305045)
-Надёжная замена OEM-пластика — предотвращает перегрев, трещины корпуса и продлевает срок службы DSG6.
-Артикул: 02E305045
-Совместимость: DSG6 02E (DQ250, мокрое сцепление), VW/Audi/Skoda/Seat (2004–2019)
-Преимущества:
-• Прочный алюминиевый корпус
-• Уплотнительное кольцо в комплекте
-Очень быстрая отправка
-Обновите корпус и убережёте DSG от перегрева</t>
+          <t>• Улучшенный отвод тепла&lt;br/&gt;&lt;br/&gt;• Уменьшает температуру масла КПП&lt;br/&gt;&lt;br/&gt;• Резиновое кольцо в комплекте&lt;br/&gt;&lt;br/&gt;🔧 Корпус фильтра АКПП DSG6 DQ250 — алюминиевый (02E305045)&lt;br/&gt;&lt;br/&gt;Алюминиевый корпус масляного фильтра заменяет пластиковый на коробках DSG6, предотвращает перегрев, деформацию и продлевает срок службы гидроблока/мехатроника&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG6 02E (DQ250, мокрое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2004–2019)&lt;br/&gt;&lt;br/&gt;• Артикул: 02E305045&lt;br/&gt;&lt;br/&gt;📌 Когда устанавливать:&lt;br/&gt;&lt;br/&gt;• Трещины, деформация OEM-корпуса&lt;br/&gt;&lt;br/&gt;• При частой замене фильтра&lt;br/&gt;&lt;br/&gt;• Если масло нагревается выше нормы&lt;br/&gt;&lt;br/&gt;💡 Преимущества:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый корпус&lt;br/&gt;&lt;br/&gt;• Уплотнение включено — сразу готов к монтажу&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Замените пластиковый корпус на более надёжный и защитите DSG от перегрева</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -656,12 +644,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП DSG7 DQ200 0AM 0CW</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии</t>
+          <t>Заглушка КПП DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая заглушка dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Заглушка дсг 7 dq200 0am 0cw всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM301212A.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -686,7 +674,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG 7 DQ200 0AM 0CW регулятор давления 1шт!</t>
+          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -761,12 +749,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM 0CW 1 шт</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -791,22 +779,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW — артикул 0AM325219C
-Крышка поддона мехатроника. Устанавливается при обслуживании DSG7 (тип DQ200). Обеспечивает герметичность и защиту внутренних элементов.
-Назначение: крышка поддона мехатроника
-Совместимость: DSG7 DQ200, мехатроники 0AM / 0CW
-Артикул: 0AM325219C
-Преимущества:
-• Подходит для плановой замены
-• Простая установка без доработок
-• Надёжная защита от пыли и масла
-Очень быстрая отправка
-Возьмите сейчас — пригодится при обслуживании или замене поддона</t>
+          <t>🔧 ОРИГИНАЛ VAG крышка мехатроника DSG7 DQ200 (0AM325219C)&lt;br/&gt;&lt;br/&gt;Герметичная крышка для мехатроника DSG7. Предотвращает утечки масла и защищает внутренние элементы от загрязнений. Подходит для коробок 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Признаки замены крышки масляного поддона мехатроника DSG7 -&lt;br/&gt;&lt;br/&gt;• Подтёки или влажность под мехатроником&lt;br/&gt;&lt;br/&gt;• Повреждение или деформация крышки&lt;br/&gt;&lt;br/&gt;• Плановая замена масла/фильтра&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас и восстановите герметичность мехатроника dq200&lt;br/&gt;&lt;br/&gt;Поддон (крышка на мехатроник) DSG 7 DQ200 0AM 0CW 0AM325219C&lt;br/&gt;&lt;br/&gt;100% новая оригинальная крышка мехатроника dq200&lt;br/&gt;&lt;br/&gt;Напрямую с завода Volkswagen&lt;br/&gt;&lt;br/&gt;Отличное качество - обеспечит качественный ремонт мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Подходит на все DQ200, если у вас DQ200 - смело заказывайте, продлите ресурс своего мехатроника!&lt;br/&gt;&lt;br/&gt;Есть также в наличии с усиленной прокладкой с утолщением. Вместе оригинальная крышка + усиленная прокладка под нее ходят намного дольше, обеспечивая максимальную герметичность мехатроника DQ200!&lt;br/&gt;&lt;br/&gt;Продаются как вместе, так и по отдельности. Заказывайте!</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -831,12 +809,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325413A.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -861,12 +839,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Улучшенный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Новый фильтр dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Для чего нужен? Для ремонта мехатроника dsg 7 dq200 0am325025 0cw</t>
+          <t>УЛУЧШЕННОЕ КАЧЕСТВО ФИЛЬТРОВ DSG7 DQ200 СМОТРИТЕ ФОТО после эксплуатации наглядна вида разница между качественным фильтром и дешевым некачественным&lt;br/&gt;&lt;br/&gt;Где используется? В мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Абсолютно новый фильтр dsg7 dq200 0am 0cw проверен в том числе на наших мехатрониках - ходит намного больше&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Фильтр мехатроника dsg 7 dq200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника dsg 7 dq200 0am325025 0cw различных модификации (подходит на все DQ200)&lt;br/&gt;&lt;br/&gt;Если вы хотите продлить ресурс вашего мехатроника и не тратится на дополнительные снятия/установки смело заказывайте наш фильтр&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325433E.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -891,13 +869,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Утолщенная прокладка крышки мехатроника DSG7 DQ200 0AM</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Утолщенная прокладка крышки мехатроника DSG7 DQ200 (артикул 0AM325443D) предназначена для герметичного соединения корпуса мехатроника на роботизированной коробке передач DSG 7 DQ 200 с  модификациями 0AM и 0CW. Усиленная прокладка используется при замене гидроблока, ревизии блока управления или устранении течи трансмиссионной жидкости.&lt;br/&gt;&lt;br/&gt;Подходит для большинства автомобилей VAG-группы (Volkswagen, Audi, Skoda, Seat), оснащённых трансмиссией DQ200. Обеспечивает надёжную герметизацию, изготовлена из термостойкого эластомера, рассчитанного на высокие нагрузки и температурные циклы.&lt;br/&gt;&lt;br/&gt;Прокладка 0AM325443D — один из ключевых элементов при ремонте мехатроника DSG 7.  Может поставляться как отдельно, так и в составе ремонтных комплектов.&lt;br/&gt;&lt;br/&gt;Прокладка для крышки мехатроника DSG7 DQ200 (0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Если у вас DQ200 то подойдет 100%. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.
-Значительно толще штатной и ходит намного дольше, заказывайте!</t>
+          <t>УСИЛЕННАЯ ПРОКЛАДКА КРЫШКИ МЕХАТРОНИКА С УТОЛЩЕНИЕМ! Прокладка для крышки мехатроника DSG7 DQ200 (артикулы 0AM / 0CW). Применяется при ремонте автоматических коробок VAG: VW, Audi, Skoda, Seat. Обеспечивает надёжную герметизацию корпуса мехатроника, исключая подтекание масла. Устанавливается по периметру алюминиевой крышки мехатроника. Устойчива к нагреву, давлению и трансмиссионной жидкости. Артикул: 0AM325443D.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -922,14 +899,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG cепараторная пластина мехатроника DSG7 DQ200</t>
+          <t>Оригинальная сепараторная пластина VAG DSG7 DQ200 0AM325467J</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J
-Отличное качество VAG
-Не гнутая, ходит намного дольше аналогов, заказывайте оригинал VAG!</t>
+          <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J&lt;br/&gt;&lt;br/&gt;Новая &lt;br/&gt;&lt;br/&gt;Отличное качество</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -954,12 +929,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды DQ200 Hilti Контрактные проверенные на стенде&lt;br/&gt;&lt;br/&gt;Минимальный пробег оригинальных соленоидов DSG7 + проверка на стенде позволяют надежно решить проблему с вышедшеми из строя соленоидами 0am 0cw.&lt;br/&gt;&lt;br/&gt;Цена указана за 4 шт - 1 половинка как на фото (1 соленоид регулятор давления + 3 Shift Шифт соленоида) контрактные б/у минимальный пробег + каждый соленоид проверяется на стенде!&lt;br/&gt;&lt;br/&gt;Всего в мехатронике устанавливаются 8 шт - 2 половинки (2 соленоида регулятора давления + 6 соленоидов Shift Шифт)&lt;br/&gt;&lt;br/&gt;Внимание - соленоиды DQ 200 качественные проверенные на стенде, если вам нужно менять полный комплект соленоидов мехатроника 0AM 8 шт - заказывайте 2 половинки по 4 шт у нас. Соленоиды Hilti как на фото - ЕСЛИ У ВАС СТОЯТ СОЛЕНОИДЫ BOSCH (с коричневым соленоидом регулятором давления) МЕНЯТЬ НУЖНО КОМПЛЕКТ ЦЕЛИКОМ - 8 БОШ на 8 БОШ, либо 8 ХИЛТИ (как у нас) на 8 ХИЛТИ. Либо если у вас стоят ХИЛТИ и вы хотите поменять 4 шт на 4 шт - так тоже можно. Не нужно ставить 4 БОШ и 4 ХИЛТИ!</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325473.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -984,12 +959,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал 0AM325587E</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60бар).  Совместимость:DSG 7 (DQ200), мехатроники 0AM/0CW Volkswagen, Audi, Skoda, Seat (2007–2023 и далее) Артикул: 0AM325587E Признаки износа/неисправности: Рывки при трогании с места Долгое задержание передач D/R Код ошибки (например, P0841) Появление металлической стружки в масле Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 Преимущества замены: Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока Отправка — максимально быстро Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1014,12 +989,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Прокладки платы DSG7 DQ200 0AM 0CW</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1044,26 +1019,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B
-Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Усиленная конструкция является надежной альтернативой пластиковому корпусу, рассчитана на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и их модификациях.
-Преимущества
-• Улучшенный отвод тепла — снижает рабочую температуру масла в КПП
-• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур
-• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек
-• Многократное использование при регламентном обслуживании
-• Оптимизированная форма с ребрами для повышения эффективности охлаждения
-Совместимость
-• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)
-• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)
-• Seat, Skoda с коробкой DQ500 (по каталогу)
-Номер детали
-0BH325183B
-Надёжная и долговечная деталь для вашей DSG7. Быстрая отправка.</t>
+          <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B&lt;br/&gt;&lt;br/&gt;🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.&lt;br/&gt;&lt;br/&gt;🔥 Преимущества:&lt;br/&gt;&lt;br/&gt;• Улучшенный отвод тепла — эффективно снижает рабочую температуру масла КПП.&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав — устойчив к деформациям, трещинам и перепадам температур.&lt;br/&gt;&lt;br/&gt;• Резиновое уплотнительное кольцо в комплекте — герметичная установка без протечек.&lt;br/&gt;&lt;br/&gt;• Многократное использование при регламентном обслуживании.&lt;br/&gt;&lt;br/&gt;• Оптимизированная форма детали с ребрами - для более эффективной работы&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B  &lt;br/&gt;&lt;br/&gt;🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1078,7 +1039,11 @@
       <c r="G19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Отмечен как серебристый вариант (был безымянным дублем 0BH325183)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1088,24 +1053,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183 B (красный)</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)
-Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надежную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Анодированное красное покрытие дополнительно защищает металл от коррозии.
-Совместимость:
-• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)
-• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)
-• Seat, Skoda с коробкой DQ500 (по каталогу)
-Номер детали: 0BH325183B
-Особенности:
-• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам
-• Анодированное красное покрытие — защита от окисления и привлекательный внешний вид
-• Полная совместимость с оригинальными уплотнительными элементами
-• Повторно используемая конструкция
-Максимально быстрая отправка.</t>
+          <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)&lt;br/&gt;&lt;br/&gt;🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.&lt;br/&gt;&lt;br/&gt;🚗 Совместимость:&lt;br/&gt;&lt;br/&gt;• Audi: RS3, TTRS, Q3, Q5 (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)&lt;br/&gt;&lt;br/&gt;• Seat, Skoda с коробкой DQ500 (по каталогу)&lt;br/&gt;&lt;br/&gt;📜 Номера детали:&lt;br/&gt;&lt;br/&gt;0BH325183B&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;• Прочный алюминиевый сплав, устойчивый к высоким температурам и нагрузкам.&lt;br/&gt;&lt;br/&gt;• Анодированное красное покрытие — дополнительная защита от окисления и привлекательный внешний вид.&lt;br/&gt;&lt;br/&gt;• Полная совместимость с оригинальными уплотнительными элементами.&lt;br/&gt;&lt;br/&gt;• Повторно используемая конструкция&lt;br/&gt;&lt;br/&gt;🚀 Закажите сейчас — максимально оперативная отправка!</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1270,12 +1223,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 Плита сальники прокладки</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 гидроплита 0AM325025</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 включает всё необходимое для ремонта и восстановления блока управления коробки передач. В комплект входят прокладка мехатроника DQ200, сальники, уплотнения, плита мехатроника и гидроплита. Совместим с трансмиссиями DSG 7 DQ200 0am и 0cw. Используется при замене гидроплиты, ремонте блока мехатроника (замене прокладок) или полной ревизии DSG. Ремкомплект подходит для большинства моделей VAG-группы (Volkswagen, Audi, Skoda, Seat) с коробкой DQ200. Детали высокого качества, проверенные временем. Прокладка крышки, комплект прокладок DSG 7, ремкомплект мехатроника купить — всё это вы найдёте в данном наборе.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1300,12 +1253,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW</t>
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. &lt;br/&gt;&lt;br/&gt;Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии гильза на мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025D.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1330,12 +1283,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200 2 пыльника 2 сальника 2 крышки</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200 пыльники крышки</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов</t>
+          <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество материалов&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025G.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1360,32 +1313,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM 0CW</t>
+          <t>Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников (как на фото) Максимально профессиональное восстановление в заводских условиях + проверка на стенде = отличный результат и гарантия работоспособности.
-без электронной платы только гидравлика
-Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.
-Для каких автомобилей подходит
-Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) 
-Audi (A1, A3, TT, Q2 и др.) 
-Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)
-Почему часто нужен ремонт / замена мехатроника DQ200
-У блока DQ200 0AM/0CW есть типичные слабые места: 
-Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.
-Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.
-Типичные симптомы:
-ошибки давления (P17BF, P189C/P1895, P06293 и др.) 
-грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях 
-Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — готовый к установке блок (без электронной платы только гидравлика)
-Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).
-Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.
-Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. 
- Что входит:
-Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, штоки, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды..
-</t>
+          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1459,43 +1392,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник DQ200 DSG7 0AM 0CW с Эл. платой</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной 0AM927769D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Каждый мехатроник DSG7 DQ200 проходит полную проверку на автомобиле после сборки.
-Мы не ограничиваемся стендовыми тестами — каждый мехатроник обязательно проходит обкатку на дороге, в реальных условиях эксплуатации. 
- • Каждый соленоид — оригинальный, проходит проверку на стенде
- • Тестирование выполняется с сопоставлением графиков с эталонными значениями, загруженными в систему
- • Любое отклонение — соленоид отбраковывается
-Используем
-Оригинальные запчасти VAG:
- • Крышка мехатроника
- • Сепараторная пластина под гидроплиту 0AM
- • Пластины соленоидов
- • Втулки штоков мехатроника DSG7 DQ200
-Усовершенствованные компоненты:
- • Усиленная прокладка крышки мехатроника (утолщенная, увеличенный ресурс)
- • Алюминиевые сальники толкателей вилок (высокое качество, не пластик и не дешевые аналоги)
- • Усиленные штоки DQ200 с дополнительной резинкой (повышенный срок службы)
- • Стальная вставка высокого качества+комплект надежных уплотнений (не теряют давление со временем)
- • Качественный ремкомплект прокладок мехатроника DSG7 DQ200
-Электронная часть:
- • Устанавливается качественная электронная плата 0AM927769D
- • Многолетний опыт производства и тестирования электронных компонентов
-Финальные испытания:
- • Каждый мехатроник проверяется на мини-стенде под давлением
- • Контроль времени сброса давления
- • Проверка работы толкателей и герметичности системы
-Главное преимущество — проверка на автомобиле:
-В отличие от большинства сервисов (99%), где мехатроник просто собирается и отдается клиенту, мы выполняем полноценную проверку DSG7 DQ200 в движении.
-Проверка на дороге — это:
- • работа всех систем под нагрузкой
- • реальное переключение передач
- • полноценная диагностика агрегата в сборе
-Только такой подход позволяет гарантировать, что мехатроник действительно исправен, а не «условно рабочий».
-Заказывайте восстановленные мехатроники DSG7 DQ200, полностью протестированные на авто, с оригинальными и улучшенными компонентами — по выгодной цене и с реальной гарантией работы.</t>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HX.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1520,7 +1422,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1550,21 +1452,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Крышка мехатроника DSG7 + прокладка поддона dq200 набор</t>
+          <t>усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ОРИГИНАЛ VAG Крышка мехатроника DSG7 DQ200 (0AM325219C) + усиленная прокладка с утолщением мехатроника DQ200 DSG7(0AM325443D)
-Комплект для восстановления герметичности масляной крышки (поддона) при обслуживании мехатроника DSG7. Подходит для 7-ступенчатой коробки с сухим сцеплением (DQ200 всех модификаций).
-Артикулы: 0AM325219C + 0AM325443D
-Совместимость: DSG7 (DQ200, 7-ступ., сухое сцепление), 0AM / 0CW, VW/Audi/Skoda/Seat
-Преимущества:
-• Точный OEM-аналог без доработок
-• Устойчив к давлению и нагреву
-Очень быстрая отправка
-Набор пригодится при плановом обслуживании или замене крышки (поддона)
-Самый эффективный и качественный вариант - оригинал VAG + усовершенствованная прокладка - лучшее и самое надежное решение </t>
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) &lt;br/&gt;&lt;br/&gt;Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: &lt;br/&gt;&lt;br/&gt;• DSG7 (DQ200, 7-ступ., сухое сцепление) &lt;br/&gt;&lt;br/&gt;• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) &lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325219C + 0AM325443D&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• Утечка или влажность под мехатроником &lt;br/&gt;&lt;br/&gt;• Снятие крышки (поддона) при ТО или замене фильтра &lt;br/&gt;&lt;br/&gt;• Деформация старой крышки или прокладки&lt;br/&gt;&lt;br/&gt;💡 Почему стоит выбрать: &lt;br/&gt;&lt;br/&gt;• OEM-аналог — точная установка без доработок &lt;br/&gt;&lt;br/&gt;• Материал выдерживает давление и температуру&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025ae.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1589,12 +1482,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Болты мехатроника DSG 7 DQ200 (0AM/0CW) комплект 7 шт.</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии</t>
+          <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.&lt;br/&gt;&lt;br/&gt;Болты мехатроника dq200 dsg 7 0am 0cw&lt;br/&gt;&lt;br/&gt;Новые болты мехатроника dsg7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Комплект болтов мехатроника dsg 7 dq200 0am 0cw - Всегда в наличии&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025f.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1619,22 +1512,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Комплект штока мехатроника DSG7 DQ200 сальник пыльник крышка</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Более 5 лет мы продаём ремкомплект с максимально усиленной плитой и собираем блоки только на нем. Решите проблему давления в мехатронике раз и навсегда. 100% качество.
-Качественный сплав — усиленная гидроплита держит давление (смотрите видео).
-Все необходимые прокладки в ремкомплекте:
-Прокладка поддона
-Фильтр мехатроника 0AM325433E, 0AM325433B
-Пыльники штоков сцепления DSG7 DQ200 0AM, 0CW, 0AM325091F, 0AM325091E
-И так далее.
-Покупая наш ремонтный комплект гидроблока DSG7 0AM/0CW, вы выполняете полноценный ремонт мехатроника, меняя все расходники и устанавливая новую усиленную гидроплиту 0AM325066AE.
-Ошибки: P17BF, P189C, P0841, P1895
-Артикулы: 0AM325025D; 0AM325025DX; 0AM325025H; 0AM325025HX; 0AM325025L; 0AM325025LX; 0AM325025M; 0AM325025MX; 0AM325025K; 0AM325025N; 0AM325025R; 0AM325026A; 0AM325026C; 0AM325025DZSN; 0AM325025DZEM.
-Заказывайте!</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1659,16 +1542,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Оригинал VAG пластины мехатроиника dsg7 dq200</t>
+          <t>пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7 + пластины на соленоиды dsg7 
-Новые ОРИГИНАЛ VAG
-Напрямую с завода
-Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)
-Оригинал Volkswagen отличное качество, ходят намного дольше, не гнутые, заказывайте!</t>
+          <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Напрямую с завода&lt;br/&gt;&lt;br/&gt;Есть как отдельно сепараторные пластины, так и в составе ремкомплекта dsg 7 (прокладки мехатроника dq200)&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025j.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1693,15 +1572,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Усиленный Новый поршень штока мехатроника DQ200 DSG 7 0AM 0CW
-Отличное качество - за счет усовершенствованной конструкции (доп резинки) ходит намного дольше
-Подходит на все штоки 0am325091E (101мм длинный) 0am325091F (99мм короткий)
-Продлите работу штоков и всего мехатроника в целом, заказывайте!</t>
+          <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идентичен оригиналу &lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1726,12 +1602,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1756,12 +1632,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт</t>
+          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH</t>
+          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1786,12 +1662,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт</t>
+          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1816,12 +1692,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025r.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1846,12 +1722,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Длинный шток 0AM325091E 101 мм+втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект Усиленный длинный шток 0AM325091E + DSG7 DQ200</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект короткий шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1876,27 +1752,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Короткий шток 0AM325091F 99 мм+втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект Усиленный короткий шток 0AM325091F + DSG7 DQ200</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DSG7 DQ200 — 0AM325091F + втулка
-Комплект: короткий шток сцепления 0AM325091F (99 мм) и гильза мехатроника DSG7 DQ200. Устраняет люфт и обеспечивает точную и надёжную работу сцепления.
-Совместимость:
-• DSG7 DQ200 (7-ступ., сухое сцепление)
-• VW / Audi / Skoda / Seat (до 2012 года)
-• Артикул штока: 0AM325091F
-Когда нужен:
-• Люфт или износ штока или втулки (гильзы)
-• Ошибки сцепления или гидроблока
-• Профилактика или ремонт мехатроника
-Особенности:
-• Шток 99 мм — точный заводской размер
-• Новая втулка — без повреждений
-• Отличное качество материалов
-Очень быстрая отправка
-Восстановите мехатроник сразу с ремкомплектом и без лишних затрат.</t>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного!</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1987,7 +1848,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2017,12 +1878,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Поршень штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество</t>
+          <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре&lt;br/&gt;&lt;br/&gt;Поршень штока мехатроника DQ200 DSG 7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый&lt;br/&gt;&lt;br/&gt;Как на фото&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2047,12 +1908,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Сальник манжет штока сцепления мехатроник DSG7 DQ200 0AM 0CW</t>
+          <t>Сальник-манжета штока сцепления DSG7 DQ200 0AM325066AD</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7</t>
+          <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новый сальник мехатроника DSG 7 DQ200 &lt;br/&gt;&lt;br/&gt;Отличное качество материала манжета мехатроника DQ200 ДСГ 7&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325066ad.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2077,29 +1938,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита DSG7 DQ200 — 0AM325066AE / 0CW
-Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW) с увеличенной толщиной стенки. Обеспечивает стабильность давления и предотвращает ошибки P17BF/P1895 и другие при интенсивной эксплуатации.
-Совместимость:
-• DSG7 DQ200 (7-ступ., сухое сцепление)
-• VW, Audi, Skoda, Seat (2007–2025)
-• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C и другие. Устанавливается на мехатроники 0AM325025H и другие варианты, а также на мехатроники 0CW.
-Особенности:
-• Увеличенная толщина стенки в зоне гидроаккумулятора
-• Хорошее качество алюминия
-Очень быстрая отправка
-Решение для тех, кто хочет надёжность без риска ошибок и поломок DSG7.
-В описании использованы запросы: плита дсг; гидроплита dsg; гидроплита мехатроника; гидроплита дсг 7; плита dq200; гидроплита dq200; плита мехатроника dsg; гидроплита dsg 7 dq200; момент затяжки гидроплиты; усиленная плита мехатроника dq200; 0am325066ae; усиленная гидроплита dsg7; усиленная плита dsg7 dq200; усиленная гидроплита dq200; усиленная плита гидроблока; усиленная плита dsg7; гидроплита dsg7 купить; замена гидроплиты dsg7. Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и другие. Устанавливается в штатное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat с коробкой DSG DQ200 0AM/0CW. Подходит для СТО и самостоятельного ремонта.
-В наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW.
-Установка данной плиты устраняет проблему с давлением в мехатронике 0AM325025 (ошибки P17BF и др.).
-Усиление стенки увеличивает ресурс мехатроника DQ200 (оригинальная плита с тонкой стенкой часто лопается).
-Сотрудничаем с заводом несколько лет.
-Отличное качество гидроплиты DQ200.
-Наша плита DSG7 не лопается и держит давление!</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2124,27 +1968,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0AM325091E</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Шток сцепления DSG7 DQ200 0AM325091E — длинный, 101 мм
-Оригинальный длинный шток (0AM325091E) для мехатроника DSG7 DQ200 0AM / 0CW. Используется в коробках dq200 старого типа (до 2012 года). Обеспечивает точную передачу усилия к муфте сцепления.
-Подходит для:
-• DSG7 DQ200 (сухое 7-ступенчатое сцепление)
-• VW, Audi, Skoda, Seat 2012–2025
-• Артикул: 0AM325091E — длинный шток 101 мм
-Когда менять:
-• При износе, деформации или нарушении передачи усилия
-• После 90 000–100 000 км или при ремонте сцепления
-• Рекомендуется менять вместе с сальниками и пыльником
-Преимущества:
-• Проверенный поставщик
-• Отличное качество, каждый шток проходит проверку
-Очень быстрая отправка
-Установите правильный новый шток — никаких лишних поездок в автосервис.
-Совместим с популярными запросами: шток мехатроника dsg 7; шток мехатроника dq200; шток дсг 7; шток сцепления dsg 7; 0am325091e; длинный шток dsg7; 101 мм шток dsg7; шток мехатроника 101 мм; замена штоков мехатроника dsg 7; установка штока dsg7; купить шток dsg7; штоки сцепления dsg; шток dsg 7 нового образца.</t>
+          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2169,26 +1998,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Шток мехатроника DSG 7 DQ200 0am325091f 99 мм короткий 1шт</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм 0AM325091F</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Шток сцепления DSG7 DQ200 0AM325091F — короткий, 99 мм
-Оригинальный шток сцепления (0AM325091F) для DSG7 DQ200 — короткий вариант на 99 мм. Используется в коробках передач до 2012 года (старого образца). Отвечает за точную работу механизма сцепления.
-Подходит для:
-• DSG7 DQ200 (7-ступ., сухая сцепа)
-• VW, Audi, Skoda, Seat (выпуск до 2012 г.)
-• Только артикул: 0AM325091F (короткий)
-Когда менять:
-• При люфте, износе, коррозии или следах масла
-• При ремонте гидроблока или полной ревизии мехатроника
-Преимущества:
-• Актуальная длина — 99 мм
-• Стабильная работа сцепления
-Очень быстрая отправка
-Проверьте длину штока и делайте заказ!
-Совместим с популярными запросами: шток мехатроника dsg 7; шток мехатроника dq200; пыльник штока мехатроника dq200; шток дсг 7; штоки мехатроника дсг 7; шток сцепления дсг 7; 0am325091f; замена штоков мехатроника dsg 7 dq200; установка мехатроника dsg 7 выставление штоков; штоки сцепления dsg; штоки сцепления dsg 7; штоки dsg 7 99 и 101; замена штоков мехатроника dsg 7; ремкомплект штоков мехатроника dsg 7; короткий шток dsg7; купить шток dsg7</t>
+          <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)&lt;br/&gt;&lt;br/&gt;Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.&lt;br/&gt;&lt;br/&gt;✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)&lt;br/&gt;&lt;br/&gt;📌 Когда ставить: &lt;br/&gt;&lt;br/&gt;• При замене вилки сцепления &lt;br/&gt;&lt;br/&gt;• При ремонте гидроблока или штока &lt;br/&gt;&lt;br/&gt;• Восстановление точности включения сцепления&lt;br/&gt;&lt;br/&gt;Точная длина 99 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка &lt;br/&gt;&lt;br/&gt;👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат&lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;•Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;•Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;•Короткие 0am325091f&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;• пыльник штока dq200&lt;br/&gt;&lt;br/&gt;• сальник штока dq200&lt;br/&gt;&lt;br/&gt;• крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;Где используется? Шток дсг 7 используется при ремонте запчасти Мехатроник dsg 7 dq200 0am 0cw&lt;br/&gt;&lt;br/&gt;У машин группы VAG все чаще встречаются проблемы со штоками мехатроника по причине больших пробегов автомобилей&lt;br/&gt;&lt;br/&gt;В идеальном состоянии и всегда в наличии штоки мехатроника DQ200 DSG 7 0am 0cw (штоки дсг 7)&lt;br/&gt;&lt;br/&gt;Есть как длинные 0am325091e, так и короткие 0am325091f&lt;br/&gt;&lt;br/&gt;Оригинал VAG штоков dq200 проходит контроль качества&lt;br/&gt;&lt;br/&gt;В штоках мехатроника дсг 7 абсолютно новые пыльник сальник и крышка штока dq200&lt;br/&gt;&lt;br/&gt;Цена указана за 1 шток dsg7&lt;br/&gt;&lt;br/&gt;👉Оформите заказ - отправим в лучшем виде!</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2213,12 +2028,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2243,19 +2058,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
-Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
-Набор защитных пыльников (чехлов) для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобилей Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений и продлевает срок службы коробки передач.
-Используется в мехатронике DSG 7 DQ200 0AM 0CW
-Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода
-Пыльник мехатроника DSG 7 всегда в наличии
-Отличное качество
-Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходников и подвержен большому износу</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2280,36 +2088,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока DQ200 DSG7 0AM Оригинал Volkswagen Германия</t>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 122390AKAF</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
-Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
-Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.
-Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.
-Применение и совместимость
-Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):
-Volkswagen
-Audi
-Skoda
-Seat
-Устанавливается в мехатроник трансмиссий с сухим сцеплением.
-Преимущества оригинальной детали Volkswagen
-Оригинальное производство Volkswagen AG (Германия)
-Точное соответствие заводским размерам
-Надёжная защита штока мехатроника
-Устойчивость к маслу, температуре и износу
-Предотвращает утечку масла и загрязнение сцепления
-Рекомендован для профессионального ремонта DSG
-Когда требуется замена пыльника
-Обнаружена утечка масла из мехатроника
-Ремонт или замена штока сцепления DSG7
-Ошибки по мехатронику DQ200
-Рывки, вибрации, нестабильная работа коробки
-Профилактика при разборке узла
-шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s</t>
+          <t xml:space="preserve"> Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)&lt;br/&gt;&lt;br/&gt;Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.&lt;br/&gt;&lt;br/&gt;Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.&lt;br/&gt;&lt;br/&gt;Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.&lt;br/&gt;&lt;br/&gt;Применение и совместимость&lt;br/&gt;&lt;br/&gt;Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):&lt;br/&gt;&lt;br/&gt;Volkswagen&lt;br/&gt;&lt;br/&gt;Audi&lt;br/&gt;&lt;br/&gt;Skoda&lt;br/&gt;&lt;br/&gt;Seat&lt;br/&gt;&lt;br/&gt;Устанавливается в мехатроник трансмиссий с сухим сцеплением.&lt;br/&gt;&lt;br/&gt;Преимущества оригинальной детали Volkswagen&lt;br/&gt;&lt;br/&gt;Оригинальное производство Volkswagen AG (Германия)&lt;br/&gt;&lt;br/&gt;Точное соответствие заводским размерам&lt;br/&gt;&lt;br/&gt;Надёжная защита штока мехатроника&lt;br/&gt;&lt;br/&gt;Устойчивость к маслу, температуре и износу&lt;br/&gt;&lt;br/&gt;Предотвращает утечку масла и загрязнение сцепления&lt;br/&gt;&lt;br/&gt;Рекомендован для профессионального ремонта DSG&lt;br/&gt;&lt;br/&gt;Когда требуется замена пыльника&lt;br/&gt;&lt;br/&gt;Обнаружена утечка масла из мехатроника&lt;br/&gt;&lt;br/&gt;Ремонт или замена штока сцепления DSG7&lt;br/&gt;&lt;br/&gt;Ошибки по мехатронику DQ200&lt;br/&gt;&lt;br/&gt;Рывки, вибрации, нестабильная работа коробки&lt;br/&gt;&lt;br/&gt;Профилактика при разборке узла&lt;br/&gt;&lt;br/&gt;шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AKAF.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2334,21 +2118,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоидов N436 / N440 DSG7 0B5 DL501</t>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B5325421</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Фильтр-сетка 123014-AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG-7 (DL501 / 0B5 / DQ500 / 0BH). Используется для тонкой фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими моделями с коробками DSG-7. Лёгкая установка, полный аналог оригинала 0B5 325 421. Отличный вариант для быстрого и недорогого восстановления работоспособности АКПП. Неоригинал высокого качества.
-Подходит для:
-• DSG-7 (DL501 / 0B5 / 0BH)
-• Устанавливается в соленоиды N436 и N440
-• Аналог оригинала 0B5 325 421
-• Обеспечивает тонкую фильтрацию масла
-• Продлевает срок службы гидроблока
-• Качественная фильтр-сетка 123014-AF
-• Идеальное решение для профилактики выхода из строя соленоидов: предотвращает засорение и продлевает ресурс КПП DQ500 / 0BH
-Фильтр-сетка соленоидов АКПП DSG7 0B5 DL501. Новая.</t>
+          <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества&lt;br/&gt;&lt;br/&gt;✅ &lt;ul&gt;&lt;li&gt;Подходит для DSG‑7 (DL501 / 0B5 / 0BH)&lt;/li&gt;&lt;li&gt;Устанавливается в соленоиды N436 / N440&lt;/li&gt;&lt;li&gt;Аналог оригинала 0B5 325 421&lt;/li&gt;&lt;li&gt;Обеспечивает тонкую фильтрацию масла&lt;/li&gt;&lt;li&gt;Продлевает срок службы гидроблока&lt;/li&gt;&lt;li&gt;Качественная фильтр‑сетка 123014‑AF&lt;/li&gt;&lt;li&gt;Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.&lt;/li&gt;&lt;/ul&gt;Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2373,30 +2148,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E Новое поколение Nissan Mitsubishi Renault</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF011E (Новое поколение) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.
-Описание товара
-Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.
-Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.
-Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.
-Когда требуется замена гидроблока
-• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим
-Преимущества
-• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП
-Совместимость
-Тип КПП: вариатор CVT Модель: JF011E / RE0F10A
-Применяется в автомобилях:
-Nissan
-Mitsubishi
-Renault
-Jeep
-(модели с установленным вариатором JF011E — по каталогу производителя)
-Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый
-гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e</t>
+          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.&lt;br/&gt;&lt;br/&gt;Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.&lt;br/&gt;&lt;br/&gt;Когда требуется замена гидроблока&lt;br/&gt;&lt;br/&gt;• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF011E / RE0F10A&lt;br/&gt;&lt;br/&gt;Применяется в автомобилях:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Jeep&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF011E — по каталогу производителя)&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2474,41 +2231,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E 1.6 Л RE0F11A Nissan, Renault, Mitsubishi</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый
-Краткое описание (первые 3 строки — самое важное для Ozon)
-Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.
-Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.
-Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.
-Признаки неисправности гидроблока JF015E:
-рывки и пинки при разгоне
-задержка включения Drive / Reverse
-пробуксовка вариатора
-переход в аварийный режим
-ошибки по давлению масла и соленоидам
-вибрации и нестабильная работа CVT
-Преимущества:
-Полная совместимость с вариатором JF015E (RE0F11A)
-Восстанавливает корректное давление масла
-Улучшает плавность хода и отклик трансмиссии
-Оптимальное решение без замены всего вариатора
-Подходит для СТО и самостоятельного ремонта
-Совместимость:
-Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)
-Часто устанавливается на:
-Nissan Juke
-Nissan Qashqai
-Nissan Note
-Nissan Sentra
-Renault Fluence
-Renault Kaptur
-Mitsubishi ASX (и другие модели с вариатором JF015E)
-Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый
-гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор</t>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый&lt;br/&gt;&lt;br/&gt;Краткое описание (первые 3 строки — самое важное для Ozon)&lt;br/&gt;&lt;br/&gt;Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.&lt;br/&gt;&lt;br/&gt;Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.&lt;br/&gt;&lt;br/&gt;Признаки неисправности гидроблока JF015E:&lt;ul&gt;&lt;li&gt;рывки и пинки при разгоне&lt;/li&gt;&lt;li&gt;задержка включения Drive / Reverse&lt;/li&gt;&lt;li&gt;пробуксовка вариатора&lt;/li&gt;&lt;li&gt;переход в аварийный режим&lt;/li&gt;&lt;li&gt;ошибки по давлению масла и соленоидам&lt;/li&gt;&lt;li&gt;вибрации и нестабильная работа CVT&lt;/li&gt;&lt;/ul&gt;Преимущества:&lt;ul&gt;&lt;li&gt;Полная совместимость с вариатором JF015E (RE0F11A)&lt;/li&gt;&lt;li&gt;Восстанавливает корректное давление масла&lt;/li&gt;&lt;li&gt;Улучшает плавность хода и отклик трансмиссии&lt;/li&gt;&lt;li&gt;Оптимальное решение без замены всего вариатора&lt;/li&gt;&lt;li&gt;Подходит для СТО и самостоятельного ремонта&lt;/li&gt;&lt;/ul&gt;Совместимость:&lt;br/&gt;&lt;br/&gt;Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)&lt;br/&gt;&lt;br/&gt;Часто устанавливается на:&lt;ul&gt;&lt;li&gt;Nissan Juke&lt;/li&gt;&lt;li&gt;Nissan Qashqai&lt;/li&gt;&lt;li&gt;Nissan Note&lt;/li&gt;&lt;li&gt;Nissan Sentra&lt;/li&gt;&lt;li&gt;Renault Fluence&lt;/li&gt;&lt;li&gt;Renault Kaptur&lt;/li&gt;&lt;li&gt;Mitsubishi ASX (и другие модели с вариатором JF015E)&lt;/li&gt;&lt;/ul&gt;Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый&lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2533,30 +2261,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E 1.8 Л RE0F11A Nissan Renault Mitsubishi</t>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
-Описание товара
-Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.
-Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.
-Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.
-Основные признаки износа гидроблока:
-• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT
-Преимущества
-• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора
-Совместимость
-Тип КПП: вариатор CVT Модель: JF015E / RE0F11A
-Подходит для автомобилей:
-Nissan
-Renault
-Mitsubishi
-(модели с установленным вариатором JF015E — по каталогу)
-Техническая информация
-Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый 
-гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan</t>
+          <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Гидроблок JF015E — основной управляющий узел вариатора CVT, отвечающий за работу соленоидов, регулировку давления масла и корректное функционирование коробки передач. Устанавливается в трансмиссии RE0F11A и применяется при ремонте вариаторов автомобилей Nissan, Renault и Mitsubishi.&lt;br/&gt;&lt;br/&gt;Неисправный гидроблок приводит к рывкам, задержкам переключений, пробуксовке и переходу коробки в аварийный режим. Замена гидроблока JF015E позволяет восстановить плавность хода, устранить ошибки CVT и вернуть стабильную работу трансмиссии без полной замены вариатора.&lt;br/&gt;&lt;br/&gt;Данный гидроблок предназначен для штатной установки и полностью совместим с конструкцией вариатора JF015E. Подходит как для профессионального ремонта на СТО, так и для частичной замены узлов при обслуживании вариатора.&lt;br/&gt;&lt;br/&gt;Основные признаки износа гидроблока:&lt;br/&gt;&lt;br/&gt;• толчки и пинки при движении • задержка включения режимов D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • аварийный режим CVT&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;• Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Тип КПП: вариатор CVT Модель: JF015E / RE0F11A&lt;br/&gt;&lt;br/&gt;Подходит для автомобилей:&lt;ul&gt;&lt;li&gt;Nissan&lt;/li&gt;&lt;li&gt;Renault&lt;/li&gt;&lt;li&gt;Mitsubishi&lt;/li&gt;&lt;/ul&gt;(модели с установленным вариатором JF015E — по каталогу)&lt;br/&gt;&lt;br/&gt;Техническая информация&lt;br/&gt;&lt;br/&gt;Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый &lt;br/&gt;&lt;br/&gt;гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2581,12 +2291,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 / 5636119</t>
+          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet&lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии&lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
+          <t>импульсная звёздочка датчика положения распредвала&lt;ul&gt;&lt;li&gt;Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.&lt;/li&gt;&lt;li&gt;Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.&lt;/li&gt;&lt;li&gt;Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)&lt;/li&gt;&lt;li&gt;Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.&lt;/li&gt;&lt;/ul&gt;Новое импульсное кольцо распредвала Opel Chevrolet &lt;br/&gt;&lt;br/&gt;Звездочка привода Распредвала - в наличии &lt;br/&gt;&lt;br/&gt;Датчик распредвала 55565480 GM</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2611,15 +2321,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра + масляный фильтр DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Комплект корпуса масляного фильтра с фильтром для роботизированной коробки передач DSG7 DQ500 (0BH).
-Подходит для автомобилей VAG с 7-ступенчатой мокрой DSG DQ500.
-Обеспечивает качественную фильтрацию масла, корпус фильтра dq500 улучшает теплоотвод и уменьшает температуру масла
-Рекомендуется при обслуживании и ремонте DSG 7 DQ500.</t>
+          <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Улучшает отвод тепла&lt;br/&gt;&lt;br/&gt;Снижает температуру масла</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2674,12 +2381,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Болт мехатроника DSG7 DQ200 0AM 0CW Длинный</t>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество</t>
+          <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный&lt;br/&gt;&lt;br/&gt;Новый Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: WHT001922.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2709,7 +2416,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).&lt;br/&gt;&lt;br/&gt; Новый, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Нужен максимальный ресурс? У нас есть улучшенная версия фильтра — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt; Артикул: filtr-dsg7-dq200.</t>
+          <t>🔧 Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).&lt;br/&gt;&lt;br/&gt;📦 Новый, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;⭐ Нужен максимальный ресурс? У нас есть улучшенная версия фильтра — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: filtr-dsg7-dq200.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2724,7 +2431,11 @@
       <c r="G61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Добавлено в основной каталог из черновика new_products.xlsx (компонент китов plita-filtr / plita-filtr-pylniki-sal). Остаток 10 шт — по вашему подтверждению.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2739,7 +2450,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. Новый, с завода, в наличии, отправка в день заказа. Артикул: 0BH325183B.</t>
+          <t>🔧 Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). ✅ Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. 📦 Новый, с завода, в наличии, отправка в день заказа. 🔩 Артикул: 0BH325183B.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2799,7 +2510,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Совместима с 0AM325219C.</t>
+          <t>🔧 Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Совместима с 0AM325219C.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2829,7 +2540,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новая, с завода, отправка в день заказа.</t>
+          <t>🔧 Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2859,7 +2570,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новые, с завода.</t>
+          <t>🔧 Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новые, с завода.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2880,12 +2591,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200,</t>
+          <t>улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита + улучшенный фильтр за один заказ. Артикул плиты 0AM325066AE. Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2910,12 +2621,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200</t>
+          <t>Плита + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Всё необходимое в одном заказе, только оригинальные расходники. Артикул плиты 0AM325066AE. Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2940,12 +2651,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, к</t>
+          <t>2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2975,7 +2686,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Нужен увеличенный ресурс? У нас есть усиленная (утолщённая) версия прокладки — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-kryshki-dq200.</t>
+          <t>🔧 Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;⭐ Нужен увеличенный ресурс? У нас есть усиленная (утолщённая) версия прокладки — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-kryshki-dq200.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3005,7 +2716,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новые, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-dq200.</t>
+          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новые, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-dq200.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3035,7 +2746,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-niz-dq200.</t>
+          <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -3061,7 +2772,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt; Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt; Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: prokladka-vtulki-verh-dq200.</t>
+          <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -3087,7 +2798,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новая, с завода, отправка в день заказа.</t>
+          <t>🔧 Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3112,12 +2823,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DS</t>
+          <t>пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt; Новые, с завода.</t>
+          <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новые, с завода.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -3143,7 +2854,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.&lt;br/&gt;&lt;br/&gt; Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.&lt;br/&gt;&lt;br/&gt; Восстановлен: проверен и протестирован перед отправкой.&lt;br/&gt;&lt;br/&gt; В наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt; Артикул: solenoid-02e-0b5-bolshoy.</t>
+          <t>🔧 Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.&lt;br/&gt;&lt;br/&gt;🔄 Восстановлен: проверен и протестирован перед отправкой.&lt;br/&gt;&lt;br/&gt;📦 В наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: solenoid-02e-0b5-bolshoy.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$76</definedName>
@@ -654,7 +654,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=7ea3564566</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=08ead15dc6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=1d88443a00|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png?v=5a785335c2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpeg?v=816487a239|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpg?v=45096a261b</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=936073c4cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.png?v=6a09eb14b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.</t>
+          <t>Масляный фильтр DQ250 DSG6 02E - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -792,7 +792,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png?v=23bde7d308</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_video.mp4?v=7ceaaba450</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="n">
         <v>2475</v>
       </c>
@@ -852,7 +856,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png?v=8bec31bf8f</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_video.mp4?v=bde8c4c289</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="n">
         <v>1250</v>
       </c>
@@ -882,7 +890,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png?v=558065bb93|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png?v=34e4e88bf6</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_video.mp4?v=6c70471405</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
         <v>1470</v>
       </c>
@@ -912,7 +924,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png?v=e49b0e06dd</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_video.mp4?v=7b0b51498e</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="n">
         <v>1400</v>
       </c>
@@ -1981,7 +1997,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png?v=9e53670a82</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="n">
         <v>2850</v>
       </c>
@@ -2011,7 +2031,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png?v=8cfd86455e</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="n">
         <v>2950</v>
       </c>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1342,7 +1342,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.png?v=6a09eb14b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_video.mp4?v=15fc20f523</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n">
         <v>85025</v>
       </c>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=e9725022b3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=68afdfa370</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=e9725022b3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=68afdfa370</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=e9725022b3</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+          <t>Прокладки электронной платы DSG7 DQ200 0AM927769N</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1025,7 +1025,11 @@
       <c r="G18" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png?v=7dfb22192b</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=08ead15dc6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=08ead15dc6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=08ead15dc6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=08ead15dc6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=08ead15dc6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_0.jpg?v=7094a0c934|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_0.jpg?v=7094a0c934|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_0.jpg?v=7094a0c934|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_0.jpg?v=7094a0c934</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_0.jpg?v=7094a0c934|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_0.jpg?v=7094a0c934</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
-        <v>675</v>
+        <v>879</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>55</v>
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>2000</v>
+        <v>5879</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>60</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>1770</v>
+        <v>1879</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>41</v>
@@ -629,7 +629,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>5000</v>
+        <v>3879</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>975</v>
+        <v>1479</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>61</v>
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>8244.5</v>
+        <v>9479</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>45</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>675</v>
+        <v>999</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>55</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2475</v>
+        <v>3479</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>45</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>675</v>
+        <v>999</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>55</v>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1250</v>
+        <v>1479</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>50</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1470</v>
+        <v>1990</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>51</v>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1400</v>
+        <v>1990</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>60</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>8784.299999999999</v>
+        <v>11979</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>11</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>9743.5</v>
+        <v>9850</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>35</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>2475</v>
+        <v>3479</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>45</v>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>10000</v>
+        <v>7979</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>10000</v>
+        <v>7979</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>10800</v>
+        <v>12890</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>40</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>2650</v>
+        <v>2890</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>47</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>3760</v>
+        <v>3879</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>53</v>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>85025</v>
+        <v>68800</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>5</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>113525</v>
+        <v>128800</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>3920</v>
+        <v>4879</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>51</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>4440</v>
+        <v>3879</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>26</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>4160</v>
+        <v>1990</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>48</v>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="n">
-        <v>1950</v>
+        <v>2879</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>61</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>1325</v>
+        <v>1490</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>47</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="n">
-        <v>8443.5</v>
+        <v>8879</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>35</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>8378.5</v>
+        <v>8979</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>35</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>41</v>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="n">
-        <v>3430</v>
+        <v>4490</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>51</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="n">
-        <v>3430</v>
+        <v>4490</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>51</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="n">
-        <v>1325</v>
+        <v>1479</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>47</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="n">
-        <v>7347.3</v>
+        <v>8879</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>43</v>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>2850</v>
+        <v>2879</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>43</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2950</v>
+        <v>2879</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>41</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="n">
-        <v>2447.15</v>
+        <v>2479</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>15</v>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="n">
-        <v>1319.7</v>
+        <v>1490</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>47</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="n">
-        <v>1225</v>
+        <v>1479</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>51</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="n">
-        <v>40052</v>
+        <v>58900</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>32</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="n">
-        <v>42408</v>
+        <v>58900</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>28</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="n">
-        <v>40052</v>
+        <v>58900</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>32</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="n">
-        <v>980</v>
+        <v>999</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>51</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="n">
-        <v>1418.1</v>
+        <v>3850</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>71</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="n">
-        <v>690</v>
+        <v>979</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>54</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="n">
-        <v>15000</v>
+        <v>12979</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>0</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2899,8 +2899,1250 @@
       </c>
       <c r="H76" s="2" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>02E927770AL</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной 02E927770AL</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. Плата уже установлена. Артикул платы 02E927770AL. Готовый узел вместо сборки из отдельных запчастей.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E927770AL_1.png?v=1ed880b735</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="n">
+        <v>118000</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>0AM927769D-plata</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="n">
+        <v>78800</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>0AM927769N</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Прокладки электронной платы DSG7 DQ200 0AM927769N</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png?v=7dfb22192b</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>0am325025x</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt; Артикул: 0am325025x.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=a1c5e406d3</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="n">
+        <v>78475</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>0am325091e-set</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. Артикул штока 0AM325091E. Усиленная версия штоков — снижает риск повторных задиров.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_1.png?v=39677a9dd4</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>8850</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>0am325091f-set</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 2 штока + 2 втулки за один заказ. Артикул штока 0AM325091F. Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png?v=6b39215af5</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>8850</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="n">
+        <v>2479</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>0cw0am</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для роботизированной коробки передач DSG 7 DQ200 поштучно маленькая . Обеспечивает надежную герметизацию электронной части мехатроника и предотвращает проникновение влаги и масла внутрь блока. Рекомендуется при любом ремонте гидравлической плиты, разборке мехатроника или появлении ошибок, связанных с электроникой TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полная герметизация электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.&lt;br/&gt;&lt;br/&gt;	•	Простая замена при обслуживании DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит как для автосервисов, так и для самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Кому подойдет&lt;br/&gt;&lt;br/&gt;Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="n">
+        <v>931</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>0cw0am325025</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Артикул: 0cw0am325025.</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png?v=b98621fc0a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png?v=e41c86e98b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025-2.png?v=45a69e38a1</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="n">
+        <v>16890</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>0cw0amdsgdq200</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt; Артикул: 0cw0amdsgdq200.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=9c731d1419</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>0cw325025h</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка электронной платы DSG7 DQ200 0AM927769N</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU. &lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением, «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания. &lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Преимущества покупки:&lt;br/&gt;&lt;br/&gt; Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt; Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt; Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt; Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt; Артикул: 0cw325025h.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png?v=ebfa02ae85</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="n">
+        <v>1290</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png?v=ff168c7b41|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png?v=78bf59e6bd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png?v=71a27c560b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png?v=ce40d7f683</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt; Артикул: Dq200dsg7.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Прокладки + сальники + пыльники DSG7 DQ200, Германия</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Артикул: Dq200dsg70am0cw.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=63685aa19d</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="n">
+        <v>8890</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. Оригинал, аналог артикула 123014AF/0B5325421. Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.png?v=995613c21a</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>gidroakkumulyator-orig</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Артикул 0AM325587E. Восстановленный оригинал VAG — отличное качество</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png?v=d4e1692d62</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="n">
+        <v>8890</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>klipsy-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. На оба штока сразу. Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.png?v=5d4d3c5107</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>planka-solenoid-2sht</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. 0AM, Volkswagen/Škoda/Audi/Seat. 2 шт за один заказ. Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.png?v=cef8cc4537</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="n">
+        <v>2890</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-orig</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.png?v=9ce5d50d5b</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="n">
+        <v>990</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита + фильтр за один заказ. Артикул плиты 0AM325066AE. Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.png?v=16f48e3b34</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита, фильтр и оба пыльника в одном заказе. Артикул плиты 0AM325066AE. Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.png?v=b85e77777e</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 пыльника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита, фильтр и оригинальные пыльники в одном заказе. Артикул плиты 0AM325066AE. Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника DQ200</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Всё необходимое в одном заказе. Артикул плиты 0AM325066AE. Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 сальника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита, фильтр и оригинальные сальники в одном заказе. Артикул плиты 0AM325066AE. Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных сальника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. Усиленный поршень — больше ресурс, чем у штатного.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Комплект на 2 штока. Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="n">
+        <v>2980</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG пыльники DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Комплект на 2 штока полностью, оригинал. Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.png?v=78bf59e6bd</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Усиленные алюминиевые сальники толкателя с 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.png?v=b11e893ec2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_2.png?v=462ec457c3</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="n">
+        <v>2490</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. На оба штока сразу. Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.png?v=ce40d7f683</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Комплект на 2 штока. Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.png?v=e1488b6f03</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Полный комплект сальников толкателей вилок DSG7 DQ200 4 шт</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 4 шт в комплекте — без поршней/толкателей, только сами сальники. Для замены сальников без разборки под замену самих толкателей.</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.png?v=36677687b8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.png?v=770b55f1cb</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>salnikprivod-l</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Сальник привода левый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. См. также правый сальник привода (отдельная позиция). Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.png?v=40460a2392</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Сальник привода правый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Сальник правого привода мехатроника/коробки DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. См. также левый сальник привода (отдельная позиция). Меняется при течи со стороны правого приводного вала.</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.png?v=7c32dc35c6</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Сальник входного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.png?v=5538a2da6a</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Сальник выходного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Сальник выходного вала коробки DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.png?v=d8d1c20493</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 4+4 деталей в одном заказе — не нужно докупать по отдельности. Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.png?v=55bef0c347</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="n">
+        <v>7400</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Комплект 4+4+4 — 12 деталей одним заказом. Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.png?v=3583dce094</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="n">
+        <v>8900</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. На оба штока сразу. Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.png?v=923daa8d8d</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="n">
+        <v>4990</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H76"/>
+  <autoFilter ref="A1:H117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Прокладки электронной платы DSG7 DQ200 0AM927769N</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Прокладка платы DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор как на фото&lt;br/&gt;&lt;br/&gt;Новые&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM927769N.</t>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>3479</v>
+        <v>78800</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>45</v>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE VAG</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW пластик 1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325477ae.</t>
+          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2075,12 +2075,16 @@
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="n">
-        <v>2479</v>
+        <v>1450</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Добавлено в основной каталог из черновика ozon_new_products.xlsx (уже продаётся на WB под этим артикулом). Остаток 13 — из заметки черновика, физически не пересчитывался.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2912,7 +2916,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. Плата уже установлена. Артикул платы 02E927770AL. Готовый узел вместо сборки из отдельных запчастей.</t>
+          <t>🔧 Мехатроник в сборе для коробки DSG6 DQ250, уже укомплектован электронной платой. ✅ Volkswagen, Škoda, Audi, Seat с DSG6 DQ250. 📦 Плата уже установлена. 🔩 Артикул платы 02E927770AL. ⭐ Готовый узел вместо сборки из отдельных запчастей.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3006,7 +3010,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt; Артикул: 0am325025x.</t>
+          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).&lt;br/&gt;&lt;br/&gt;Новые соленоиды Bosch&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор&lt;br/&gt;&lt;br/&gt;Новые ремкомплект и прокладки dq200&lt;br/&gt;&lt;br/&gt;Втулки, штоки, сальники, пыльники, крышка мехатроника&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Надежный поставщик - восстанавливается в заводских условиях, проверяется на специализированном оборудовании после сборки на давление&lt;br/&gt;&lt;br/&gt;Мехатроник идет без электронной платы (гидравлическая часть), просто перекручиваете свою эл плату если она в порядке или ставите другую и также прикручиваете к нашему мехатронику.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025x.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3036,7 +3040,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. Артикул штока 0AM325091E. Усиленная версия штоков — снижает риск повторных задиров.</t>
+          <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3070,7 +3074,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 2 штока + 2 втулки за один заказ. Артикул штока 0AM325091F. Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3164,7 +3168,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Артикул: 0cw0am325025.</t>
+          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Состав комплекта&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Усиленная гидравлическая плита — 0AM325066AE&lt;br/&gt;&lt;br/&gt;	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенная надёжность за счёт усиленной гидроплиты.&lt;br/&gt;&lt;br/&gt;	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Устранение течей по штокам и снижение риска повторных неисправностей.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0am325025.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3194,7 +3198,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt; Артикул: 0cw0amdsgdq200.</t>
+          <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Обеспечивает плотную и надежную герметизацию электронной платы.&lt;br/&gt;&lt;br/&gt;	•	Снижает риск коррозии контактов и отказов электронного блока.&lt;br/&gt;&lt;br/&gt;	•	Удобна в установке при техническом обслуживании и ремонте DSG.&lt;br/&gt;&lt;br/&gt;	•	Подходит для использования в автосервисах и при самостоятельном ремонте.&lt;br/&gt;&lt;br/&gt;Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3224,7 +3228,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU. &lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением, «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания. &lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Преимущества покупки:&lt;br/&gt;&lt;br/&gt; Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt; Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt; Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt; Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt; Артикул: 0cw325025h.</t>
+          <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔎&lt;br/&gt;&lt;br/&gt;Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📌 Совместимость:&lt;br/&gt;&lt;br/&gt;	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔧 Особенности:&lt;br/&gt;&lt;br/&gt;	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.&lt;br/&gt;&lt;br/&gt;	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;📦 Преимущества покупки:&lt;br/&gt;&lt;br/&gt;✔ Быстрая и простая замена при обслуживании мехатроника&lt;br/&gt;&lt;br/&gt;✔ Совместима с популярными моделями VAG-группы&lt;br/&gt;&lt;br/&gt;✔ Низкая цена по сравнению с полным комплектом прикладок блока мехатроника&lt;br/&gt;&lt;br/&gt;✔ Подходит как для самостоятельного ремонта, так и для сервисных центров&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;⭐ Кому подойдет:&lt;br/&gt;&lt;br/&gt;Эта прокладка идеально подходит для автосервисов, диагностов и автолюбителей, которые выполняют ремонт или обслуживание механических и электронных узлов DSG-коробки DQ200, а также тюнинг и восстановление мехатроника.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔍 Почему это важно:&lt;br/&gt;&lt;br/&gt;При разборке мехатроника DSG без новой прокладки хорошего качества возрастает риск попадания жидкости внутрь платы управления, что может привести к коррозии контактов, сбоям в работе TCU и дорогостоящему ремонту. Прокладка 0AM927377 позволяет избежать подобных проблем.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0cw325025h.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3254,7 +3258,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM</t>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.&lt;br/&gt;&lt;br/&gt;Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.&lt;br/&gt;&lt;br/&gt;Оригинальная деталь Volkswagen изготавливается из термостойкого и маслостойкого эластомера, рассчитанного на рабочие температуры и давление мехатроника DQ200. Обеспечивает точную посадку на шток, плотное прилегание и длительный срок службы без потери эластичности.&lt;br/&gt;&lt;br/&gt;Сальник рекомендуется к замене при проведении планового обслуживания, ремонте мехатроника, ревизии гидроблока или при обнаружении следов масла в зоне штока сцепления. Полностью совместим с оригинальными штоками мехатроника и устанавливается в штатное посадочное место без доработок.&lt;br/&gt;&lt;br/&gt;Использование оригинального сальника Volkswagen позволяет сохранить заводские параметры работы DSG7, избежать повторных разборок и снизить риск дорогостоящего ремонта сцепления и мехатроника.&lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;DSG7 DQ200 (7-ступенчатая коробка с сухим сцеплением) Мехатроник 0AM / 0CW Автомобили Volkswagen, Audi, Skoda, Seat&lt;br/&gt;&lt;br/&gt;Назначение&lt;br/&gt;&lt;br/&gt;Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7&lt;br/&gt;&lt;br/&gt;Преимущества оригинала&lt;br/&gt;&lt;br/&gt;• Оригинальная деталь Volkswagen &lt;br/&gt;&lt;br/&gt;• Точная заводская геометрия &lt;br/&gt;&lt;br/&gt;• Устойчивость к температуре и давлению &lt;br/&gt;&lt;br/&gt;• Длительный ресурс эксплуатации &lt;br/&gt;&lt;br/&gt;• Установка без доработок&lt;br/&gt;&lt;br/&gt;Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0сц.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3284,7 +3288,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt; Артикул: Dq200dsg7.</t>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3309,12 +3313,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники DSG7 DQ200, Германия</t>
+          <t>пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt; Артикул: Dq200dsg70am0cw.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Описание товара&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Комплектация&lt;br/&gt;&lt;br/&gt;	•	Прокладка крышки мехатроника — 0AM325443D&lt;br/&gt;&lt;br/&gt;	•	Крышка мехатроника — 0AM325219C&lt;br/&gt;&lt;br/&gt;	•	Фильтр мехатроника — 0AM325433E&lt;br/&gt;&lt;br/&gt;	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D&lt;br/&gt;&lt;br/&gt;	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)&lt;br/&gt;&lt;br/&gt;И так далее как на фото! &lt;br/&gt;&lt;br/&gt;Совместимость&lt;br/&gt;&lt;br/&gt;Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;Преимущества&lt;br/&gt;&lt;br/&gt;	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.&lt;br/&gt;&lt;br/&gt;	•	Повышенный ресурс за счёт усиленной гидравлической плиты.&lt;br/&gt;&lt;br/&gt;	•	Оригинальные сальники и пыльники Volkswagen (Германия).&lt;br/&gt;&lt;br/&gt;	•	Минимизация риска повторных утечек и отказов.&lt;br/&gt;&lt;br/&gt;	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;&lt;br/&gt;🔩 Артикул: Dq200dsg70am0cw.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3344,7 +3348,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. Оригинал, аналог артикула 123014AF/0B5325421. Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3374,7 +3378,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Артикул 0AM325587E. Восстановленный оригинал VAG — отличное качество</t>
+          <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3404,7 +3408,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. На оба штока сразу. Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3434,7 +3438,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. 0AM, Volkswagen/Škoda/Audi/Seat. 2 шт за один заказ. Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3459,12 +3463,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200</t>
+          <t>Оригинальные пластины на соленоиды VAG DSG7 DQ200 без</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3489,12 +3493,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр DSG7 DQ200, комплект</t>
+          <t>фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита + фильтр за один заказ. Артикул плиты 0AM325066AE. Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3519,12 +3523,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200</t>
+          <t>фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита, фильтр и оба пыльника в одном заказе. Артикул плиты 0AM325066AE. Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3549,12 +3553,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 пыльника DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита, фильтр и оригинальные пыльники в одном заказе. Артикул плиты 0AM325066AE. Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3579,12 +3583,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника DQ200</t>
+          <t>фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Всё необходимое в одном заказе. Артикул плиты 0AM325066AE. Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -3609,12 +3613,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 сальника DSG7 DQ200, комплект</t>
+          <t>фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Плита, фильтр и оригинальные сальники в одном заказе. Артикул плиты 0AM325066AE. Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -3644,7 +3648,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -3674,7 +3678,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. Усиленный поршень — больше ресурс, чем у штатного.</t>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Комплект на 2 штока. Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -3734,7 +3738,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Комплект на 2 штока полностью, оригинал. Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -3764,7 +3768,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -3794,7 +3798,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -3824,7 +3828,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. На оба штока сразу. Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -3854,7 +3858,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Комплект на 2 штока. Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -3884,7 +3888,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 4 шт в комплекте — без поршней/толкателей, только сами сальники. Для замены сальников без разборки под замену самих толкателей.</t>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -3914,7 +3918,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. См. также правый сальник привода (отдельная позиция). Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -3944,7 +3948,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Сальник правого привода мехатроника/коробки DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. См. также левый сальник привода (отдельная позиция). Меняется при течи со стороны правого приводного вала.</t>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -3974,7 +3978,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4004,7 +4008,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Сальник выходного вала коробки DSG7 DQ200. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4034,7 +4038,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4059,12 +4063,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200</t>
+          <t>4 сальника DSG7 DQ200, на весь мехатроник</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 4+4 деталей в одном заказе — не нужно докупать по отдельности. Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4089,12 +4093,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные DSG7 DQ200</t>
+          <t>усиленные алюминиевые сальники DSG7 DQ200, комплект 4 + 4</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. Комплект 4+4+4 — 12 деталей одним заказом. Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4124,7 +4128,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. 0AM/0CW, Volkswagen/Škoda/Audi/Seat. На оба штока сразу. Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png?v=3fb6a6ed69</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_1.png?v=3fb6a6ed69</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png?v=ff168c7b41|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png?v=78bf59e6bd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png?v=71a27c560b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png?v=ce40d7f683</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.png?v=ff168c7b41|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_4.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_5.png?v=78bf59e6bd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_6.png?v=71a27c560b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_7.png?v=ce40d7f683</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="n">
-        <v>1450</v>
+        <v>2450</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>15</v>
@@ -2961,7 +2961,11 @@
       <c r="G78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2677,7 +2677,11 @@
       <c r="G68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Ozon: нет (дубль SPU / не создаём)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2707,7 +2711,11 @@
       <c r="G69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Ozon: нет (дубль SPU / не создаём)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2901,7 +2909,11 @@
       <c r="G76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Пока не продаём</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3517,7 +3529,11 @@
       <c r="G96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Ozon: нет (дубль SPU / не создаём)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3667,7 +3683,11 @@
       <c r="G101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Ozon: нет (дубль SPU / не создаём)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3697,7 +3717,11 @@
       <c r="G102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Ozon: нет (дубль SPU / не создаём)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3757,7 +3781,11 @@
       <c r="G104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Ozon: нет (дубль SPU / не создаём)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3787,7 +3815,11 @@
       <c r="G105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Ozon: нет (дубль SPU / не создаём)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -798,12 +798,16 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3479</v>
+        <v>4130</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -896,12 +900,16 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1990</v>
+        <v>2540</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1491,12 +1499,16 @@
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>4879</v>
+        <v>6050</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1701,12 +1713,16 @@
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>980</v>
+        <v>1240</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1731,12 +1747,16 @@
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>1479</v>
+        <v>1880</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1942,17 +1962,21 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="n">
-        <v>980</v>
+        <v>1240</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2011,12 +2035,16 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>2879</v>
+        <v>3620</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2139,12 +2167,16 @@
       </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="n">
-        <v>1490</v>
+        <v>1620</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3134,12 +3166,16 @@
       </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="n">
-        <v>2479</v>
+        <v>2860</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3159,7 +3195,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=f1652abe3c</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -3254,12 +3290,16 @@
       </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="n">
-        <v>1290</v>
+        <v>1610</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Цена поднята 22.10.2026 для выхода из эластичного бустинга Ozon</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie комплект 4</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=a1c5e406d3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=7f59b31f49</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.png?v=ff168c7b41|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_4.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_5.png?v=78bf59e6bd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_6.png?v=71a27c560b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_7.png?v=ce40d7f683</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.png?v=197acf8189|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.png?v=ff168c7b41|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.png?v=78bf59e6bd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_4.png?v=71a27c560b</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4221,8 +4221,38 @@
       </c>
       <c r="H117" s="2" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. Артикул 0BH325159. Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png?v=207791c0ab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png?v=33f6b91718</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H117"/>
+  <autoFilter ref="A1:H118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. Артикул 0BH325159. Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="n">
-        <v>0</v>
+        <v>3879</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>0</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2618,7 +2618,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="n">
-        <v>490</v>
+        <v>990</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="n">
-        <v>980</v>
+        <v>1490</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="n">
-        <v>490</v>
+        <v>990</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>0</v>
@@ -2910,7 +2910,7 @@
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="n">
-        <v>1870</v>
+        <v>2290</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="n">
-        <v>990</v>
+        <v>1690</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>0</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="n">
-        <v>999</v>
+        <v>1490</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>0</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="n">
-        <v>999</v>
+        <v>1490</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="n">
-        <v>999</v>
+        <v>1490</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="n">
-        <v>999</v>
+        <v>1490</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="n">
-        <v>1950</v>
+        <v>2790</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>0</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="n">
-        <v>8879</v>
+        <v>6990</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>43</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
-        <v>879</v>
+        <v>950</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>55</v>
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>5879</v>
+        <v>5850</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>60</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>1879</v>
+        <v>1850</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>41</v>
@@ -629,7 +629,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>3879</v>
+        <v>3850</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>1479</v>
+        <v>1350</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>61</v>
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>9479</v>
+        <v>9350</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>45</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>55</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4130</v>
+        <v>4350</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>45</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>55</v>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1479</v>
+        <v>1350</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>50</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2540</v>
+        <v>2350</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>51</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1990</v>
+        <v>1850</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>60</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>11979</v>
+        <v>11850</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>11</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>7979</v>
+        <v>7850</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>7979</v>
+        <v>7850</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>12890</v>
+        <v>12850</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>40</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>2890</v>
+        <v>2850</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>47</v>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>3879</v>
+        <v>3850</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>53</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>68800</v>
+        <v>68850</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>5</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>128800</v>
+        <v>128850</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>5</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>980</v>
+        <v>950</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>51</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>6050</v>
+        <v>6350</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>51</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>3879</v>
+        <v>3850</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>26</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>1990</v>
+        <v>1850</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>48</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="n">
-        <v>2879</v>
+        <v>2850</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>61</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>47</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="n">
-        <v>8879</v>
+        <v>8850</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>35</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>8979</v>
+        <v>8850</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>35</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>1240</v>
+        <v>1350</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>51</v>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>1880</v>
+        <v>1850</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>41</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="n">
-        <v>4490</v>
+        <v>4350</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>51</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="n">
-        <v>4490</v>
+        <v>4350</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>51</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="n">
-        <v>980</v>
+        <v>950</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>51</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="n">
-        <v>1479</v>
+        <v>1350</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>47</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="n">
-        <v>1240</v>
+        <v>1350</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>51</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="n">
-        <v>6990</v>
+        <v>6850</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>43</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>3620</v>
+        <v>3850</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>43</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2879</v>
+        <v>2850</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>41</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="n">
-        <v>2450</v>
+        <v>2350</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>15</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="n">
-        <v>980</v>
+        <v>950</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>51</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="n">
-        <v>1620</v>
+        <v>1850</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>47</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="n">
-        <v>1479</v>
+        <v>1350</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>51</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="n">
-        <v>58900</v>
+        <v>58850</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>32</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="n">
-        <v>58900</v>
+        <v>58850</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>28</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="n">
-        <v>58900</v>
+        <v>58850</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>32</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="n">
-        <v>999</v>
+        <v>950</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>51</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="n">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>54</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="n">
-        <v>980</v>
+        <v>950</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="n">
-        <v>1290</v>
+        <v>1350</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="n">
-        <v>12979</v>
+        <v>12850</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>0</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="n">
-        <v>1950</v>
+        <v>1850</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="n">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="n">
-        <v>7500</v>
+        <v>7850</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="n">
-        <v>9500</v>
+        <v>9850</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>0</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="n">
-        <v>8500</v>
+        <v>8850</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="n">
-        <v>1380</v>
+        <v>1350</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="n">
-        <v>840</v>
+        <v>950</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="n">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>0</v>
@@ -2910,7 +2910,7 @@
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="n">
-        <v>2290</v>
+        <v>2350</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="n">
-        <v>5700</v>
+        <v>5850</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="n">
-        <v>118000</v>
+        <v>118850</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="n">
-        <v>78800</v>
+        <v>78850</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="n">
-        <v>3479</v>
+        <v>3350</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="n">
-        <v>78475</v>
+        <v>78850</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>0</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="n">
-        <v>2860</v>
+        <v>2850</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>0</v>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="n">
-        <v>931</v>
+        <v>950</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="n">
-        <v>16890</v>
+        <v>16850</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="n">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>0</v>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="n">
-        <v>1610</v>
+        <v>1850</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="n">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="n">
-        <v>8890</v>
+        <v>8850</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="n">
-        <v>8890</v>
+        <v>8850</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>0</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="n">
-        <v>2890</v>
+        <v>2850</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="n">
-        <v>1690</v>
+        <v>1850</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>0</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="n">
-        <v>7500</v>
+        <v>7850</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="n">
-        <v>8500</v>
+        <v>8850</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="n">
-        <v>8500</v>
+        <v>8850</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="n">
-        <v>9500</v>
+        <v>9850</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="n">
-        <v>8500</v>
+        <v>8850</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="n">
-        <v>9500</v>
+        <v>9850</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>0</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="n">
-        <v>3990</v>
+        <v>3850</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="n">
-        <v>2980</v>
+        <v>2850</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>0</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>0</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="n">
-        <v>2490</v>
+        <v>2350</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="n">
-        <v>1690</v>
+        <v>1850</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="n">
-        <v>1890</v>
+        <v>1850</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="n">
-        <v>1950</v>
+        <v>1850</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>0</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>0</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="n">
-        <v>2790</v>
+        <v>2850</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="n">
-        <v>7400</v>
+        <v>7350</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="n">
-        <v>8900</v>
+        <v>8850</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>0</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="n">
-        <v>4990</v>
+        <v>4850</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="n">
-        <v>3879</v>
+        <v>3850</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>0</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -3000,7 +3000,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="n">
-        <v>78850</v>
+        <v>74850</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>0</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>128850</v>
+        <v>118850</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>5</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>5850</v>
+        <v>5350</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>60</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="n">
-        <v>3850</v>
+        <v>4850</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>71</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра ребристый DSG7 DQ500 0BH325183B, красный</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="n">
-        <v>7850</v>
+        <v>7350</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>0</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Корпус фильтра ребристый DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>6350</v>
+        <v>4850</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>51</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1296,7 +1296,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>2850</v>
+        <v>3350</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>47</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>51</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2850</v>
+        <v>3350</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>41</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 02E - отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.</t>
+          <t>⚙️ Масляный фильтр мехатроника DSG6 DQ250 02E305051C — новый, отличное качество.&lt;br/&gt;&lt;br/&gt;✅ Устанавливается в коробки DSG6 02E (DQ250) на VW, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🛠 Рекомендуется менять при каждой замене масла в коробке DSG6.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 02E305051C.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.</t>
+          <t>⚙️ Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N — новый соленоид Bosch, отличное качество.&lt;br/&gt;&lt;br/&gt;✅ Подходит для мехатроников 0AM и 0CW коробки DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;🛠 Применяется при ремонте мехатроника: рывки, ошибки и сбои переключения передач.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025n.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Новое&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;Всегда в наличии</t>
+          <t>⚙️ Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C — новое, отличное качество.&lt;br/&gt;&lt;br/&gt;✅ Подходит для мехатроников 0AM и 0CW коробки DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;🛠 Применяется при ремонте мехатроника и замене гидроаккумулятора: устраняет утечку и падение давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025С.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии&lt;br/&gt;&lt;br/&gt;Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.</t>
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq200 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.&lt;br/&gt;&lt;br/&gt;Полный комплект прокладки dsg 7 dq200 0am как на фото&lt;br/&gt;&lt;br/&gt;Полный комплект для ремонта мехатроника DSG 7 DQ200 0AM 0CW Ремкомплект мехатроника DSG 7 DQ200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Как на фото: фильтр мехатроника, пыльники штоков, сепараторная пластина, прокладка поддона и все другие необходимые прокладки мехатроника&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025m.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW&lt;br/&gt;&lt;br/&gt;Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).&lt;br/&gt;&lt;br/&gt;Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW&lt;br/&gt;&lt;br/&gt;Установка данной плиты ДСГ7 решает проблему c давлением в мехатронике 0am325025 (ошибки P17BF и т.д.).&lt;br/&gt;&lt;br/&gt;Усиление стенки увеличивает ресурс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -754,12 +754,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.</t>
+          <t>⚙️ Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A (0AM, 0CW) — новая, отличное качество.&lt;br/&gt;&lt;br/&gt;✅ Закрывает отверстие мехатроника при снятии, хранении и перевозке: защищает от грязи и влаги.&lt;br/&gt;&lt;br/&gt;🛠 Пригодится при ремонте DSG7 и отправке блока.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0AM325120A.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_0.jpg?v=7094a0c934</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=8c1fd99eb1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -963,7 +963,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW&lt;br/&gt;&lt;br/&gt;Новая&lt;br/&gt;&lt;br/&gt;Отличное качество&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.</t>
+          <t>⚙️ Крышка штока мехатроника DSG7 DQ200 0AM325025Q (0AM, 0CW) — новая, отличное качество.&lt;br/&gt;&lt;br/&gt;✅ Подходит для мехатроников коробки DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;🛠 Применяется при ремонте мехатроника и замене штоков, сальников и пыльников.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025q.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -968,12 +968,16 @@
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>11850</v>
+        <v>12850</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 11850 → 12850 (прибыль Ozon ≥ ~80% закупки; через 1–2 недели проверить продажи)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2001,12 +2005,16 @@
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="n">
-        <v>6850</v>
+        <v>7850</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 6850 → 7850 (прибыль Ozon ≥ ~80% закупки; через 1–2 недели проверить продажи)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2674,12 +2682,16 @@
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="n">
-        <v>7850</v>
+        <v>8850</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 7850 → 8850 (прибыль Ozon ≥ ~80% закупки; через 1–2 недели проверить продажи)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -509,12 +509,16 @@
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -659,12 +663,16 @@
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -764,12 +772,16 @@
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -832,12 +844,16 @@
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -963,7 +979,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1473,12 +1489,16 @@
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1627,12 +1647,16 @@
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1911,12 +1935,16 @@
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1941,12 +1969,16 @@
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2145,12 +2177,16 @@
       </c>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2209,12 +2245,16 @@
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2407,7 +2447,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2472,12 +2512,16 @@
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2502,14 +2546,14 @@
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Добавлено в основной каталог из черновика new_products.xlsx (компонент китов plita-filtr / plita-filtr-pylniki-sal). Остаток 10 шт — по вашему подтверждению.</t>
+          <t>Добавлено в основной каталог из черновика new_products.xlsx (компонент китов plita-filtr / plita-filtr-pylniki-sal). Остаток 10 шт — по вашему подтверждению.; 27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
         </is>
       </c>
     </row>
@@ -2536,12 +2580,16 @@
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2596,12 +2644,16 @@
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1850 → 2350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2626,12 +2678,16 @@
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2784,12 +2840,16 @@
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2814,12 +2874,16 @@
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2896,12 +2960,16 @@
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3212,12 +3280,16 @@
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3272,12 +3344,16 @@
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3336,12 +3412,16 @@
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3366,12 +3446,16 @@
       </c>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3486,12 +3570,16 @@
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 950 → 1350 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3862,14 +3950,14 @@
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Ozon: нет (дубль SPU / не создаём)</t>
+          <t>Ozon: нет (дубль SPU / не создаём); 27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4104,16 @@
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4046,12 +4138,16 @@
       </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4076,12 +4172,16 @@
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4106,12 +4206,16 @@
       </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -663,14 +663,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>61</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27.10.2026: цена 1350 → 1850 (мин. 400 ₽ чистыми на Ozon)</t>
+          <t>27.10.2026: закупка 100 ₽, цена оставлена 1350 (~385 ₽ чистыми на Ozon)</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -979,7 +979,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2904,12 +2904,16 @@
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 450 → 950 (на 450 Ozon был в минусе)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2930,12 +2934,16 @@
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2026: цена 450 → 950 (на 450 Ozon был в минусе)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -979,7 +979,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=6e4db825ca</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2893,15 +2893,19 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>Черное кольцо-прокладка втулки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на нижнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=c467de34e5</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="n">
         <v>950</v>
@@ -2923,15 +2927,19 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>Зеленое кольцо-прокладка втулки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на верхнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=9ac6f4aac3</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="n">
         <v>950</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2864,12 +2864,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новые, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-dq200.</t>
+          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0am325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новые, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-dq200.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=6e4db825ca</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=8312c47b41</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на нижнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
+          <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на нижнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=c467de34e5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=b00fa3937b</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -2932,12 +2932,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на верхнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
+          <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на верхнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=9ac6f4aac3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=28c553abfe</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_0.jpg?v=7094a0c934</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_0.jpg?v=94573cf68b</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0am325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новые, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-dq200.</t>
+          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (зеленое + черное) — уплотняют посадку втулки, предотвращают потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новые, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-dq200.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=8312c47b41</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=e3f97523c1</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на нижнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
+          <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=b00fa3937b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=6c730c6907</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -2932,12 +2932,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на верхнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
+          <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все гильзы (втулки) штоков.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=28c553abfe</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=f7366cb6a0</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2705,7 +2705,11 @@
           <t>🔧 Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-dq200-2sht_1.png?v=98c47f4555</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="n">
         <v>1350</v>
@@ -3003,7 +3007,11 @@
           <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastiny-solenoid-dq200_1.png?v=6b8ccfb635</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="n">
         <v>2350</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2783,7 +2783,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Ozon: нет (дубль SPU / не создаём)</t>
+          <t>Ozon: нет (дубль SPU / не создаём); 27.10.2026: Ozon «нет» — дубль существующей карточки (SPU)</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Ozon: нет (дубль SPU / не создаём)</t>
+          <t>Ozon: нет (дубль SPU / не создаём); 27.10.2026: Ozon «нет» — дубль существующей карточки (SPU)</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Ozon: нет (дубль SPU / не создаём)</t>
+          <t>Ozon: нет (дубль SPU / не создаём); 27.10.2026: Ozon «нет» — дубль существующей карточки (SPU)</t>
         </is>
       </c>
     </row>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1807,7 +1807,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png?v=c48648e856</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="n">
         <v>5350</v>
       </c>
@@ -1837,7 +1841,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="n">
         <v>4350</v>
       </c>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -979,7 +979,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>12850</v>
+        <v>13850</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>40</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="n">
-        <v>7850</v>
+        <v>9850</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>43</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="n">
-        <v>8850</v>
+        <v>10850</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="n">
-        <v>9850</v>
+        <v>11850</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>0</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="n">
-        <v>8850</v>
+        <v>10850</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="n">
-        <v>16850</v>
+        <v>17850</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>0</v>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="n">
-        <v>7350</v>
+        <v>9350</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="n">
-        <v>8850</v>
+        <v>10850</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>0</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="n">
-        <v>8850</v>
+        <v>10850</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="n">
-        <v>9850</v>
+        <v>11850</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="n">
-        <v>8850</v>
+        <v>10850</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>0</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="n">
-        <v>9850</v>
+        <v>11850</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>0</v>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="WB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WB'!$A$1:$H$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -4399,8 +4399,68 @@
       </c>
       <c r="H118" s="2" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>0AM927769F</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769F</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769F Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7&lt;br/&gt;&lt;br/&gt;Описание:&lt;br/&gt;&lt;br/&gt;Электронная плата мехатроника DSG7 DQ200 0AM927769F для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.&lt;br/&gt;&lt;br/&gt;Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.&lt;br/&gt;&lt;br/&gt;OEM: подходит только если на родной плате такой номер 0AM927769F 0AM 927 769 F &lt;br/&gt;&lt;br/&gt;Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769F</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_1.png?v=866128ed82</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="n">
+        <v>74850</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>0am325025HXF</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной 0AM927769F</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен.</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_1.png?v=098d4c588e|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_2.png?v=838071f395|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_3.png?v=b93ad38a77</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="n">
+        <v>118850</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H118"/>
+  <autoFilter ref="A1:H120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -4442,7 +4442,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен.</t>
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. &lt;br/&gt;&lt;br/&gt;Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)&lt;br/&gt;&lt;br/&gt;В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - &lt;br/&gt;&lt;br/&gt;Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Усовершенствованные &lt;br/&gt;&lt;br/&gt;Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)&lt;br/&gt;&lt;br/&gt;Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)&lt;br/&gt;&lt;br/&gt;Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)&lt;br/&gt;&lt;br/&gt;Качественный ремкомплект прокладок мехатроника DSG7 DQ200 &lt;br/&gt;&lt;br/&gt;Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. &lt;br/&gt;&lt;br/&gt;Электронная плата отличного качества, многолетний опыт производства и тестирования&lt;br/&gt;&lt;br/&gt;В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) &lt;br/&gt;&lt;br/&gt;И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. &lt;br/&gt;&lt;br/&gt;Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. &lt;br/&gt;&lt;br/&gt;Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!&lt;br/&gt;&lt;br/&gt;🔌 Электронная плата: 0AM927769F (0AM 927 769 F). Перед заказом сверьте номер платы на вашем мехатронике или пришлите VIN — подберём.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025HXF.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -4270,7 +4270,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.png?v=d8d1c20493</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_video.mp4?v=c4a1d424d7</t>
+        </is>
+      </c>
       <c r="F114" s="2" t="n">
         <v>2850</v>
       </c>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1975,7 +1975,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png?v=997df2de75</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="n">
         <v>1850</v>
       </c>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -4018,7 +4018,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.png?v=b11e893ec2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_2.png?v=462ec457c3</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_video.mp4?v=bbf75624cd</t>
+        </is>
+      </c>
       <c r="F106" s="2" t="n">
         <v>2350</v>
       </c>
@@ -4338,7 +4342,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.png?v=3583dce094</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_video.mp4?v=bbf75624cd</t>
+        </is>
+      </c>
       <c r="F116" s="2" t="n">
         <v>8850</v>
       </c>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1457,7 +1457,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png?v=4ec9bb8ca0|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png?v=838071f395|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png?v=b93ad38a77</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_video.mp4?v=15fc20f523</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="n">
         <v>118850</v>
       </c>
@@ -4466,7 +4470,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_1.png?v=098d4c588e|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_2.png?v=838071f395|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_3.png?v=b93ad38a77</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_video.mp4?v=15fc20f523</t>
+        </is>
+      </c>
       <c r="F120" s="2" t="n">
         <v>118850</v>
       </c>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -543,12 +543,16 @@
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>5350</v>
+        <v>3350</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>28.10.2026: цена 5350 → 3350 (красный индекс Ozon, 0 продаж)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -633,12 +637,16 @@
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>3850</v>
+        <v>2350</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>28.10.2026: цена 3850 → 2350 (красный индекс Ozon, 0 продаж)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -979,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1082,14 +1090,14 @@
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>7850</v>
+        <v>4350</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Отмечен как серебристый вариант (был безымянным дублем 0BH325183)</t>
+          <t>Отмечен как серебристый вариант (был безымянным дублем 0BH325183); 28.10.2026: цена 7850 → 4350 (красный индекс Ozon, 0 продаж)</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1124,16 @@
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>7850</v>
+        <v>4350</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>28.10.2026: цена 7850 → 4350 (красный индекс Ozon, 0 продаж)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2014,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2463,17 +2475,21 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="n">
-        <v>4850</v>
+        <v>3850</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>28.10.2026: цена 4850 → 3850 (красный индекс Ozon, 0 продаж)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3127,7 +3143,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>28.10.2026: Цена WB 78800 → 74850 (WB = Ozon)</t>
         </is>
       </c>
     </row>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -3134,7 +3134,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_video.mp4?v=843d5fd39f</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="n">
         <v>74850</v>
       </c>
@@ -4456,7 +4460,11 @@
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_1.png?v=866128ed82</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_video.mp4?v=843d5fd39f</t>
+        </is>
+      </c>
       <c r="F119" s="2" t="n">
         <v>74850</v>
       </c>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png?v=1d34e63372</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png?v=1d34e63372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_2.png?v=05bb8a9d17|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_3.png?v=cf9c379a2d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_4.png?v=ba95dc8cc4|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_5.png?v=35342b3570</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpeg?v=816487a239|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpg?v=45096a261b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpeg?v=816487a239|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png?v=0a275c4f18|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_3.png?v=9f571585c3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_4.png?v=2ec99b161d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_5.png?v=fce0696edd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_6.png?v=19f05c95c1</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект&lt;br/&gt;&lt;br/&gt;Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.</t>
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, 1 шт&lt;br/&gt;&lt;br/&gt;Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Пыльник (чехол) защитный для штока толкателя мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.&lt;br/&gt;&lt;br/&gt;✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!&lt;br/&gt;&lt;br/&gt;✔️Пыльник мехатроника DSG 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;✔️Отличное качество&lt;br/&gt;&lt;br/&gt;✔️ Пыльник штока сцепления DSG 7 DQ200 необходим для ремонта мехатроника DSG 7, так как относится к категории расходники и подвержен большому износу!&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.png?v=6a09eb14b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.png?v=6a09eb14b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_3.png?v=b93ad38a77|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=2c2ec12303|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_2.png?v=6165752180|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_3.png?v=bd6892c018|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_4.png?v=cfa7b1abb1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_5.png?v=58f7e9e533</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1016,12 +1016,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) &lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. &lt;/li&gt;&lt;li&gt;Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). &lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM/0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Признаки износа/неисправности:&lt;ul&gt;&lt;li&gt;Рывки при трогании с места&lt;/li&gt;&lt;li&gt;Долгое задержание передач D/R&lt;/li&gt;&lt;li&gt;Код ошибки (например, P0841)&lt;/li&gt;&lt;li&gt;Появление металлической стружки в масле&lt;/li&gt;&lt;li&gt;Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 &lt;/li&gt;&lt;/ul&gt;💡 Преимущества замены:&lt;ul&gt;&lt;li&gt;Снижает риск повреждения мехатроника и сцепления&lt;/li&gt;&lt;li&gt;Увеличивает ресурс гидроблока&lt;/li&gt;&lt;/ul&gt;📦 Отправка — максимально быстро&lt;br/&gt;&lt;br/&gt;Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.&lt;br/&gt;&lt;br/&gt;Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.&lt;br/&gt;&lt;br/&gt;Номер 0am325587e&lt;br/&gt;&lt;br/&gt;Отличное качество гидроаккумулятора дсг7&lt;br/&gt;&lt;br/&gt;Гидроаккумулятор dsg 7 всегда в наличии&lt;br/&gt;&lt;br/&gt;Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E)&lt;br/&gt;&lt;br/&gt;📦 Назначение:&lt;ul&gt;&lt;li&gt;Хранит запас давления масла в гидравлике мехатроника DSG7 DQ200 и обеспечивает быстрое срабатывание сцеплений и переключение передач.&lt;/li&gt;&lt;li&gt;Газовый (азотный) гидроаккумулятор, устанавливается в штатное место в гидроплите мехатроника.&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;DSG 7 (DQ200), мехатроники 0AM / 0CW&lt;/li&gt;&lt;li&gt;Volkswagen, Audi, Skoda, Seat&lt;/li&gt;&lt;li&gt;Артикул: 0AM325587E&lt;/li&gt;&lt;/ul&gt;📌 Когда проверяют гидроаккумулятор:&lt;ul&gt;&lt;li&gt;Ошибки P17BF / P189C — давление в гидравлике мехатроника не держится, насос работает дольше обычного&lt;/li&gt;&lt;/ul&gt;Такие же ошибки бывают при трещине гидроплиты и износе уплотнений. Точную причину показывает диагностика давления и времени работы насоса мехатроника.&lt;br/&gt;&lt;br/&gt;🔧 Уплотнительное кольцо — в комплекте (как на фото).&lt;br/&gt;&lt;br/&gt;Новый гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW) — Volkswagen, Audi, Skoda, Seat. Номер 0am325587e.&lt;br/&gt;&lt;br/&gt;📦 Отправка — максимально быстро</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png?v=32561fb4b6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_5.png?v=21c2aff101</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png?v=32561fb4b6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_5.png?v=21c2aff101</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_4.png?v=20cf9233ba|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_5.png?v=ef6024ff7f</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!&lt;br/&gt;&lt;br/&gt;Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpeg?v=816487a239|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png?v=0a275c4f18|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_3.png?v=9f571585c3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_4.png?v=2ec99b161d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_5.png?v=fce0696edd|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_6.png?v=19f05c95c1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpeg?v=816487a239|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png?v=0a275c4f18|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_3.png?v=9f571585c3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_4.png?v=2ec99b161d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_5.png?v=325f3a05a7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_6.png?v=19f05c95c1</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C/P1895, P06293 и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
+          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! &lt;br/&gt;&lt;br/&gt;Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.&lt;br/&gt;&lt;br/&gt;БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА&lt;br/&gt;&lt;br/&gt;Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.&lt;br/&gt;&lt;br/&gt;Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. &lt;br/&gt;&lt;br/&gt;✅ Для каких автомобилей подходит&lt;ul&gt;&lt;li&gt;Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) &lt;/li&gt;&lt;li&gt;Audi (A1, A3, TT, Q2 и др.) &lt;/li&gt;&lt;li&gt;Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)&lt;/li&gt;&lt;/ul&gt;⚠️ Почему часто нужен ремонт / замена мехатроника DQ200&lt;br/&gt;&lt;br/&gt;У блока DQ200 0AM/0CW есть типичные слабые места: &lt;ul&gt;&lt;li&gt;Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.&lt;/li&gt;&lt;li&gt;Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.&lt;/li&gt;&lt;/ul&gt;Типичные симптомы:&lt;ul&gt;&lt;li&gt;ошибки давления (P17BF, P189C и др.) &lt;/li&gt;&lt;li&gt;грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях &lt;/li&gt;&lt;li&gt;«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи&lt;/li&gt;&lt;/ul&gt;⚙️ Почему стоит купить именно этот мехатроник&lt;ul&gt;&lt;li&gt;Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.&lt;/li&gt;&lt;li&gt;Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)&lt;/li&gt;&lt;li&gt;Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).&lt;/li&gt;&lt;li&gt;Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.&lt;/li&gt;&lt;li&gt;Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. &lt;/li&gt;&lt;/ul&gt;📦 Что входит:&lt;ul&gt;&lt;li&gt;Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее&lt;/li&gt;&lt;/ul&gt;📣 Почему стоит выбрать нас&lt;br/&gt;&lt;br/&gt;Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025H.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW&lt;br/&gt;&lt;br/&gt;Установка данной плиты ДСГ7 решает проблему c давлением в мехатронике 0am325025 (ошибки P17BF и т.д.).&lt;br/&gt;&lt;br/&gt;Усиление стенки увеличивает ресурс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P189C и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW&lt;br/&gt;&lt;br/&gt;Установка данной плиты ДСГ7 решает проблему c давлением в мехатронике 0am325025 (ошибки P17BF и т.д.).&lt;br/&gt;&lt;br/&gt;Усиление стенки увеличивает ресурс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P189C и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок гидроплита (P17BF, P1895 и др.)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW&lt;br/&gt;&lt;br/&gt;Установка данной плиты ДСГ7 решает проблему c давлением в мехатронике 0am325025 (ошибки P17BF и т.д.).&lt;br/&gt;&lt;br/&gt;Усиление стенки увеличивает ресурс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
+          <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW&lt;br/&gt;&lt;br/&gt;Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P189C и тд при интенсивной эксплуатации.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2007–2025)&lt;br/&gt;&lt;br/&gt;• Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C&lt;br/&gt;&lt;br/&gt;📌 Когда ставить:&lt;br/&gt;&lt;br/&gt;• OEM‑плита деформирована или треснула&lt;br/&gt;&lt;br/&gt;• При появлении ошибок давления (P17BF, P189C)&lt;br/&gt;&lt;br/&gt;• В условиях городской езды или частого переключения передач&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7&lt;br/&gt;&lt;br/&gt;Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Убирает ошибки давления P17BF, P189C, если их причина — трещина штатной плиты. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw&lt;br/&gt;&lt;br/&gt;🔩 Подходит для СТО и самостоятельного ремонта.&lt;br/&gt;&lt;br/&gt;Всегда в наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW&lt;br/&gt;&lt;br/&gt;Установка данной плиты ДСГ7 решает проблему c давлением в мехатронике 0am325025 (ошибки P17BF и т.д.).&lt;br/&gt;&lt;br/&gt;Усиление стенки увеличивает ресурс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).&lt;br/&gt;&lt;br/&gt;Сотрудничаем с заводом несколько лет&lt;br/&gt;&lt;br/&gt;Отличное качество гидроплиты dq200&lt;br/&gt;&lt;br/&gt;Наша плита dsg 7 не лопается и держит давление!&lt;br/&gt;&lt;br/&gt;📌 Главное - простукивайте шарики при установке!!!</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -915,7 +915,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png?v=558065bb93|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png?v=34e4e88bf6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png?v=558065bb93|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png?v=34e4e88bf6|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_3.png?v=085537cd98|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_4.png?v=0b19e411db</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png?v=997df2de75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png?v=997df2de75|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_2.png?v=134a867769|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_3.png?v=1f9c1db793</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png?v=9e53670a82</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.png?v=9e53670a82</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png?v=8cfd86455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.png?v=8cfd86455e</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_2.png?v=63faeb51e1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_3.png?v=58af8d5194</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1849,12 +1849,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (до 2012 г)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Ошибки сцепления / гидроблока&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного!</t>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного!</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_2.png?v=ceee164228|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_3.png?v=2ca83e0e5a</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png?v=7dfb22192b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png?v=7dfb22192b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png?v=f94ab6c512|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_3.png?v=efe35124f0</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png?v=7dfb22192b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png?v=7dfb22192b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_2.png?v=f94ab6c512|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_3.png?v=efe35124f0</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (до 2012 года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (примерно с 2012 модельного года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (примерно до 2012 модельного года) — ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;⚠️ Не путайте длинный 101 мм (0AM325091E) и короткий 99 мм (0AM325091F) — сверяйте длину старого штока и год машины&lt;br/&gt;&lt;br/&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного!</t>
+          <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!&lt;br/&gt;&lt;br/&gt;Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7 ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW/Audi/Skoda/Seat (примерно с 2012 модельного года)&lt;br/&gt;&lt;br/&gt;• Артикул штока: 0AM325091F&lt;br/&gt;&lt;br/&gt;📌 Когда нужен:&lt;br/&gt;&lt;br/&gt;• Люфт или износ штока или втулки (гильзы)&lt;br/&gt;&lt;br/&gt;• Профилактика или ремонт мехатроника&lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Шток 99 мм — точный, заводской размер&lt;br/&gt;&lt;br/&gt;⚠️ Не путайте длинный 101 мм (0AM325091E) и короткий 99 мм (0AM325091F) — сверяйте длину старого штока и год машины&lt;br/&gt;&lt;br/&gt;• Новая втулка — без царапин и задиров&lt;br/&gt;&lt;br/&gt;• Отличное качество материалов&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Восстановите мехатроник сразу с ремкомплектом и без лишних затрат&lt;br/&gt;&lt;br/&gt;🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного!</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (2012–2025)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, новый тип)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Проблемы при включении передач&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.&lt;br/&gt;&lt;br/&gt;В наличии оригинальные штоки DSG7 DQ200 0AM 0CW&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!</t>
+          <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)&lt;br/&gt;&lt;br/&gt;Длинный шток 101 мм первого поколения для DSG7 DQ200 (0AM/0CW) — автомобили примерно до 2012 модельного года (мехатроник 0AM325025D). Обеспечивает точную и стабильную работу сцепления и коробки передач в целом&lt;br/&gt;&lt;br/&gt;✅ Совместимость:&lt;br/&gt;&lt;br/&gt;• DSG7 DQ200 (7‑ступ., сухое сцепление)&lt;br/&gt;&lt;br/&gt;• VW, Audi, Skoda, Seat (примерно до 2012 модельного года)&lt;br/&gt;&lt;br/&gt;• Артикул: 0AM325091E (длинный шток, первое поколение)&lt;br/&gt;&lt;br/&gt;📌 Заменять, если:&lt;br/&gt;&lt;br/&gt;• Появился люфт, коррозия или выработка&lt;br/&gt;&lt;br/&gt;• Планируется плановый ремонт мехатроника &lt;br/&gt;&lt;br/&gt;💡 Особенности:&lt;br/&gt;&lt;br/&gt;• Длина — 101 мм&lt;br/&gt;&lt;br/&gt;⚠️ Не путайте длинный 101 мм (0AM325091E) и короткий 99 мм (0AM325091F) — сверяйте длину старого штока и год машины&lt;br/&gt;&lt;br/&gt;📦 Очень быстрая отправка&lt;br/&gt;&lt;br/&gt;👉 Обновите шток и увеличьте ресурс мехатроника &lt;br/&gt;&lt;br/&gt;Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7.&lt;br/&gt;&lt;br/&gt;Идеальное состояние - каждый шток дсг 7 dq200 проверяется&lt;br/&gt;&lt;br/&gt;Штоки dq200 всегда в наличии&lt;br/&gt;&lt;br/&gt;Длинные 0am325091e&lt;br/&gt;&lt;br/&gt;📌Шток dsg 7 с уже установленными новыми запчастями:&lt;br/&gt;&lt;br/&gt;•пыльник штока dq200&lt;br/&gt;&lt;br/&gt;•сальник штока dq200&lt;br/&gt;&lt;br/&gt;•крышка штока dsg 7&lt;br/&gt;&lt;br/&gt;📦 Делайте заказ - отправим моментально!</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1593,12 +1593,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация:&lt;ul&gt;&lt;li&gt;Сальник штока&lt;/li&gt;&lt;li&gt;Пыльник штока&lt;/li&gt;&lt;li&gt;Крышка штока&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (примерно с 2012 модельного года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (примерно до 2012 модельного года) — ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;⚠️ Не путайте длинный 101 мм (0AM325091E) и короткий 99 мм (0AM325091F) — сверяйте длину старого штока и год машины&lt;br/&gt;&lt;br/&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.</t>
+          <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)&lt;br/&gt;&lt;br/&gt;Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.&lt;br/&gt;&lt;br/&gt;📦 Комплектация (на оба штока):&lt;ul&gt;&lt;li&gt;Сальник штока — 2 шт.&lt;/li&gt;&lt;li&gt;Пыльник штока — 2 шт.&lt;/li&gt;&lt;li&gt;Крышка штока — 2 шт.&lt;/li&gt;&lt;/ul&gt;✅ Совместимость:&lt;ul&gt;&lt;li&gt;Коробка DSG 7 DQ200&lt;/li&gt;&lt;li&gt;Мехатроники с кодами 0AM, 0CW&lt;/li&gt;&lt;li&gt;Штоки:&lt;ul&gt;&lt;li&gt;0AM325091F — короткий, 99 мм (примерно с 2012 модельного года)&lt;/li&gt;&lt;li&gt;0AM325091E — длинный, 101 мм (примерно до 2012 модельного года) — ремкомплект подходит на оба типа&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;⚠️ Не путайте длинный 101 мм (0AM325091E) и короткий 99 мм (0AM325091F) — сверяйте длину старого штока и год машины&lt;br/&gt;&lt;br/&gt;💡 Почему стоит купить:&lt;ul&gt;&lt;li&gt;Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200&lt;/li&gt;&lt;li&gt;Подходит для профилактики и ремонта&lt;/li&gt;&lt;li&gt;Не требует специнструмента — подходит для самостоятельной замены&lt;/li&gt;&lt;/ul&gt;📦 Высылаем быстро&lt;br/&gt;&lt;br/&gt;👉 Готов к установке — бери и ставь без лишней головной боли&lt;br/&gt;&lt;br/&gt;В комплекте на 2 штока&lt;br/&gt;&lt;br/&gt;Пыльник штока dq200 — 2 шт.&lt;br/&gt;&lt;br/&gt;Сальник штока dsg7 — 2 шт.&lt;br/&gt;&lt;br/&gt;Крышка штока мехатроника — 2 шт.&lt;br/&gt;&lt;br/&gt;Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. &lt;br/&gt;&lt;br/&gt;Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.&lt;br/&gt;&lt;br/&gt;Идеален для технического обслуживания и увеличения срока службы мехатроника.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: 0am325025h.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=7cb0bd4a20</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=c580346d11|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_3.png?v=93a1d5f63e</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200 сальник пыльник</t>
+          <t>Ремкомплект 2 штоков DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=c580346d11|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_3.png?v=93a1d5f63e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=00f749e742|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_3.png?v=93a1d5f63e</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200 2 сальника 2 2</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=00f749e742|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_3.png?v=93a1d5f63e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=00f749e742|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_3.png?v=b4d863de86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_2.png?v=63faeb51e1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_3.png?v=58af8d5194</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_2.png?v=c9edf3be30|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_3.png?v=2df80504df</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_2.png?v=ceee164228|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_3.png?v=2ca83e0e5a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_2.png?v=ceee164228|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_3.png?v=1a52462bed</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Соленоид регулятор давления DSG7 DQ200</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Клипса штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения Shift DSG7 DQ200 0AM325025N</t>
+          <t>Соленоид переключения Shift DSG7 DQ200</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Крышка штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM325025R</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png?v=462ec457c3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png?v=67c3826247|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_2.png?v=2d9991cda7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_3.png?v=fe9eae47d4</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>1850</v>
+        <v>3850</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>48</v>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Соленоид переключения Shift DSG7 DQ200</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=e80f5309a2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.png?v=483a3c950f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_3.png?v=65fcd1abc4</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_1.png?v=866128ed82</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_1.png?v=866128ed82|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_2.png?v=dc60c0af48|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_3.png?v=92286a8a02</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">

--- a/data/wb_catalog.xlsx
+++ b/data/wb_catalog.xlsx
@@ -3203,7 +3203,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=7f59b31f49</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=01d97a7972</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
